--- a/Dataset_inf.xlsx
+++ b/Dataset_inf.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="10480"/>
+    <workbookView windowWidth="28800" windowHeight="12280"/>
   </bookViews>
   <sheets>
     <sheet name="Label" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1266" uniqueCount="455">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1282" uniqueCount="465">
   <si>
     <t>Note</t>
   </si>
@@ -285,6 +285,39 @@
     <t>P19</t>
   </si>
   <si>
+    <t>Claus Lamm</t>
+  </si>
+  <si>
+    <t>claus.lamm@univie.ac.at</t>
+  </si>
+  <si>
+    <t>Bukowski et al.</t>
+  </si>
+  <si>
+    <t>Friend</t>
+  </si>
+  <si>
+    <t>Age, IRI, cEQ, PANAS</t>
+  </si>
+  <si>
+    <t>2 (two consecutive days)</t>
+  </si>
+  <si>
+    <t>Laboratory paired testing, participants in adjacent independent rooms</t>
+  </si>
+  <si>
+    <t>Austria</t>
+  </si>
+  <si>
+    <t>Vienna</t>
+  </si>
+  <si>
+    <t>4(Imitation-Inhibition, Imitation, Inhibitory-Control, Being-Imitated)×2(Affective Touch-Congruency:Congruent, Incongruent)×2(Affective Touch-Perspective:Self, Other)×3(Shape-Matching-Label:Self, Friend, Stranger)</t>
+  </si>
+  <si>
+    <t>Affective Touch: rose/feather/worm/slug (visuo-tactile stimuli); Shape-Matching: triangle/square/circle (visual shapes); Training Task: hand finger movements (visual stimuli)</t>
+  </si>
+  <si>
     <t>Bukowski_2021_AP</t>
   </si>
   <si>
@@ -349,9 +382,6 @@
   </si>
   <si>
     <t>Human Brain Mapping</t>
-  </si>
-  <si>
-    <t>Friend</t>
   </si>
   <si>
     <t>Netherlands</t>
@@ -799,7 +829,7 @@
     <t>Frequency (Self &gt; Friend)</t>
   </si>
   <si>
-    <t>2(StimulusFrequency:self-frequent,friend-frequent)*2(ShapeAssociation:self,friend)*2(MatchingCondi_x0002_tion:matching,nonmatching)</t>
+    <t>2(StimulusFrequency:self-frequent,friend-frequent)*2(ShapeAssociation:self,friend)*2(MatchingCondition:matching,nonmatching)</t>
   </si>
   <si>
     <t>Pn16E3</t>
@@ -1596,7 +1626,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1608,6 +1638,12 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
       <charset val="134"/>
     </font>
     <font>
@@ -2136,16 +2172,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2154,46 +2187,49 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2205,7 +2241,7 @@
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2217,7 +2253,7 @@
     <xf numFmtId="0" fontId="0" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2229,7 +2265,7 @@
     <xf numFmtId="0" fontId="0" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2241,7 +2277,7 @@
     <xf numFmtId="0" fontId="0" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2253,7 +2289,7 @@
     <xf numFmtId="0" fontId="0" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2266,7 +2302,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2282,13 +2318,16 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
@@ -2297,25 +2336,25 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="6">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="6" applyFont="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="6" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="6" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -2324,13 +2363,13 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
@@ -2679,13 +2718,13 @@
     <col min="15" max="16" width="9" customWidth="1"/>
     <col min="17" max="17" width="20.0833333333333" customWidth="1"/>
     <col min="18" max="18" width="21.5833333333333" customWidth="1"/>
-    <col min="19" max="19" width="13.0833333333333" customWidth="1"/>
+    <col min="19" max="19" width="17.8333333333333" customWidth="1"/>
     <col min="20" max="20" width="14.25" customWidth="1"/>
     <col min="21" max="21" width="12.9166666666667" customWidth="1"/>
     <col min="22" max="22" width="13.25" customWidth="1"/>
     <col min="23" max="23" width="41.6666666666667" customWidth="1"/>
     <col min="24" max="24" width="29" customWidth="1"/>
-    <col min="25" max="25" width="28.4166666666667" style="6" customWidth="1"/>
+    <col min="25" max="25" width="28.4166666666667" style="7" customWidth="1"/>
     <col min="26" max="26" width="14.5" customWidth="1"/>
     <col min="27" max="27" width="17.5833333333333" customWidth="1"/>
     <col min="28" max="28" width="14.5" customWidth="1"/>
@@ -2694,14 +2733,14 @@
     <col min="31" max="31" width="9.925" customWidth="1"/>
     <col min="32" max="32" width="12.75" customWidth="1"/>
     <col min="33" max="33" width="7.58333333333333" customWidth="1"/>
-    <col min="34" max="34" width="118.833333333333" customWidth="1"/>
+    <col min="34" max="34" width="87.375" customWidth="1"/>
     <col min="35" max="36" width="25.75" customWidth="1"/>
     <col min="37" max="37" width="59.425" customWidth="1"/>
     <col min="38" max="38" width="68.6416666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="5" customFormat="1" ht="15.5" spans="1:296">
-      <c r="A1" s="5" t="s">
+    <row r="1" s="6" customFormat="1" ht="15.5" spans="1:296">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -2807,10 +2846,10 @@
       <c r="AJ1" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="AK1" s="5" t="s">
+      <c r="AK1" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="AL1" s="5" t="s">
+      <c r="AL1" s="6" t="s">
         <v>36</v>
       </c>
     </row>
@@ -2827,22 +2866,22 @@
       <c r="D2" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="F2" s="8">
+      <c r="F2" s="9">
         <v>1</v>
       </c>
-      <c r="G2" s="9">
+      <c r="G2" s="10">
         <v>0</v>
       </c>
-      <c r="H2" s="9">
+      <c r="H2" s="10">
         <v>0</v>
       </c>
       <c r="I2" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="J2" s="10" t="s">
+      <c r="J2" s="11" t="s">
         <v>42</v>
       </c>
       <c r="K2" s="4" t="s">
@@ -2918,7 +2957,7 @@
       <c r="AJ2" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="AK2" s="11" t="s">
+      <c r="AK2" s="12" t="s">
         <v>54</v>
       </c>
       <c r="AL2" s="4"/>
@@ -3194,20 +3233,20 @@
       <c r="D3" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="F3" s="8">
+      <c r="F3" s="9">
         <v>1</v>
       </c>
-      <c r="G3" s="9">
+      <c r="G3" s="10">
         <v>0</v>
       </c>
-      <c r="H3" s="9">
+      <c r="H3" s="10">
         <v>0</v>
       </c>
       <c r="I3" s="4"/>
-      <c r="J3" s="10"/>
+      <c r="J3" s="11"/>
       <c r="K3" s="4" t="s">
         <v>43</v>
       </c>
@@ -3281,7 +3320,7 @@
       <c r="AJ3" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="AK3" s="10" t="s">
+      <c r="AK3" s="11" t="s">
         <v>54</v>
       </c>
       <c r="AL3" s="4"/>
@@ -3557,20 +3596,20 @@
       <c r="D4" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="F4" s="8">
+      <c r="F4" s="9">
         <v>1</v>
       </c>
-      <c r="G4" s="9">
+      <c r="G4" s="10">
         <v>0</v>
       </c>
-      <c r="H4" s="9">
+      <c r="H4" s="10">
         <v>0</v>
       </c>
       <c r="I4" s="4"/>
-      <c r="J4" s="10"/>
+      <c r="J4" s="11"/>
       <c r="K4" s="4" t="s">
         <v>43</v>
       </c>
@@ -3644,7 +3683,7 @@
       <c r="AJ4" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="AK4" s="10" t="s">
+      <c r="AK4" s="11" t="s">
         <v>54</v>
       </c>
       <c r="AL4" s="4"/>
@@ -3920,20 +3959,20 @@
       <c r="D5" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="F5" s="8">
+      <c r="F5" s="9">
         <v>1</v>
       </c>
-      <c r="G5" s="9">
+      <c r="G5" s="10">
         <v>0</v>
       </c>
-      <c r="H5" s="9">
+      <c r="H5" s="10">
         <v>0</v>
       </c>
       <c r="I5" s="4"/>
-      <c r="J5" s="10"/>
+      <c r="J5" s="11"/>
       <c r="K5" s="4" t="s">
         <v>43</v>
       </c>
@@ -3998,14 +4037,16 @@
         <f>AC5-AF5</f>
         <v>40</v>
       </c>
-      <c r="AH5" s="4"/>
+      <c r="AH5" s="4" t="s">
+        <v>51</v>
+      </c>
       <c r="AI5" s="4" t="s">
         <v>52</v>
       </c>
       <c r="AJ5" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="AK5" s="10" t="s">
+      <c r="AK5" s="11" t="s">
         <v>54</v>
       </c>
       <c r="AL5" s="4"/>
@@ -4281,22 +4322,22 @@
       <c r="D6" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="F6" s="8">
+      <c r="F6" s="9">
         <v>1</v>
       </c>
-      <c r="G6" s="9">
+      <c r="G6" s="10">
         <v>0</v>
       </c>
-      <c r="H6" s="9">
+      <c r="H6" s="10">
         <v>0</v>
       </c>
       <c r="I6" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="J6" s="10" t="s">
+      <c r="J6" s="11" t="s">
         <v>42</v>
       </c>
       <c r="K6" s="4" t="s">
@@ -4367,7 +4408,7 @@
         <f>AC6-AF6</f>
         <v>92</v>
       </c>
-      <c r="AH6" s="4" t="s">
+      <c r="AH6" s="13" t="s">
         <v>72</v>
       </c>
       <c r="AI6" s="4" t="s">
@@ -4376,7 +4417,7 @@
       <c r="AJ6" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="AK6" s="10" t="s">
+      <c r="AK6" s="11" t="s">
         <v>74</v>
       </c>
       <c r="AL6" s="4"/>
@@ -4639,7 +4680,7 @@
       <c r="KI6" s="4"/>
       <c r="KJ6" s="4"/>
     </row>
-    <row r="7" ht="15.5" spans="1:296">
+    <row r="7" ht="124" spans="1:296">
       <c r="A7" s="4"/>
       <c r="B7" s="4">
         <v>6</v>
@@ -4650,41 +4691,101 @@
       <c r="D7" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="E7" s="7"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="4"/>
-      <c r="J7" s="10"/>
-      <c r="K7" s="4"/>
-      <c r="L7" s="4"/>
-      <c r="M7" s="4"/>
-      <c r="N7" s="4"/>
-      <c r="O7" s="4"/>
-      <c r="P7" s="4"/>
-      <c r="Q7" s="4"/>
-      <c r="R7" s="4"/>
-      <c r="S7" s="4"/>
-      <c r="T7" s="4"/>
-      <c r="U7" s="4"/>
-      <c r="V7" s="4"/>
-      <c r="W7" s="4"/>
-      <c r="X7" s="4"/>
-      <c r="Y7" s="4"/>
-      <c r="Z7" s="4"/>
-      <c r="AA7" s="4"/>
-      <c r="AB7" s="4"/>
-      <c r="AC7" s="4"/>
-      <c r="AD7" s="4"/>
-      <c r="AE7" s="4"/>
-      <c r="AF7" s="4"/>
-      <c r="AG7" s="4"/>
-      <c r="AH7" s="4"/>
-      <c r="AI7" s="4"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="9">
+        <v>1</v>
+      </c>
+      <c r="G7" s="10">
+        <v>1</v>
+      </c>
+      <c r="H7" s="10">
+        <v>0</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L7" s="4">
+        <v>2021</v>
+      </c>
+      <c r="M7" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="N7" s="4">
+        <v>1</v>
+      </c>
+      <c r="O7" s="4">
+        <v>1</v>
+      </c>
+      <c r="P7" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q7" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="R7" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="S7" s="4">
+        <v>12</v>
+      </c>
+      <c r="T7" s="4">
+        <v>1</v>
+      </c>
+      <c r="U7" s="4">
+        <v>180</v>
+      </c>
+      <c r="V7" s="4">
+        <v>3</v>
+      </c>
+      <c r="W7" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="X7" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="Y7" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z7" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="AA7" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="AB7" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="AC7" s="4">
+        <v>132</v>
+      </c>
+      <c r="AD7" s="4">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="4">
+        <v>132</v>
+      </c>
+      <c r="AF7" s="4">
+        <v>42</v>
+      </c>
+      <c r="AG7" s="4">
+        <v>90</v>
+      </c>
+      <c r="AH7" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="AI7" s="13" t="s">
+        <v>87</v>
+      </c>
       <c r="AJ7" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="AK7" s="11"/>
+        <v>88</v>
+      </c>
+      <c r="AK7" s="4"/>
       <c r="AL7" s="4"/>
       <c r="AM7" s="4"/>
       <c r="AN7" s="4"/>
@@ -4951,17 +5052,23 @@
         <v>7</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="E8" s="7"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="9">
+        <v>1</v>
+      </c>
+      <c r="G8" s="10">
+        <v>1</v>
+      </c>
+      <c r="H8" s="10">
+        <v>0</v>
+      </c>
       <c r="I8" s="4"/>
-      <c r="J8" s="10"/>
+      <c r="J8" s="11"/>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
       <c r="M8" s="4"/>
@@ -4988,9 +5095,9 @@
       <c r="AH8" s="4"/>
       <c r="AI8" s="4"/>
       <c r="AJ8" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="AK8" s="11"/>
+        <v>88</v>
+      </c>
+      <c r="AK8" s="12"/>
       <c r="AL8" s="4"/>
       <c r="AM8" s="4"/>
       <c r="AN8" s="4"/>
@@ -5257,37 +5364,37 @@
         <v>8</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="E9" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="E9" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="F9" s="8">
+      <c r="F9" s="9">
         <v>1</v>
       </c>
-      <c r="G9" s="9">
+      <c r="G9" s="10">
         <v>0</v>
       </c>
-      <c r="H9" s="9">
+      <c r="H9" s="10">
         <v>0</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="J9" s="10" t="s">
-        <v>82</v>
+        <v>92</v>
+      </c>
+      <c r="J9" s="11" t="s">
+        <v>93</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="L9" s="4">
         <v>2020</v>
       </c>
       <c r="M9" s="4" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="N9" s="4">
         <v>1</v>
@@ -5300,7 +5407,7 @@
       </c>
       <c r="Q9" s="4"/>
       <c r="R9" s="4" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="S9" s="4">
         <v>48</v>
@@ -5317,16 +5424,16 @@
       <c r="W9" s="4"/>
       <c r="X9" s="4"/>
       <c r="Y9" s="4" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="Z9" s="4" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="AA9" s="4" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="AB9" s="4" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="AC9" s="4">
         <v>46</v>
@@ -5349,10 +5456,10 @@
         <v>52</v>
       </c>
       <c r="AJ9" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="AK9" s="11" t="s">
-        <v>91</v>
+        <v>101</v>
+      </c>
+      <c r="AK9" s="12" t="s">
+        <v>102</v>
       </c>
       <c r="AL9" s="4"/>
       <c r="AM9" s="4"/>
@@ -5616,43 +5723,43 @@
     </row>
     <row r="10" ht="31" spans="1:296">
       <c r="A10" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="B10" s="4">
         <v>9</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="E10" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="E10" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="F10" s="8">
+      <c r="F10" s="9">
         <v>1</v>
       </c>
-      <c r="G10" s="9">
+      <c r="G10" s="10">
         <v>0</v>
       </c>
-      <c r="H10" s="8">
+      <c r="H10" s="9">
         <v>1</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="J10" s="10" t="s">
-        <v>96</v>
+        <v>106</v>
+      </c>
+      <c r="J10" s="11" t="s">
+        <v>107</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="L10" s="4">
         <v>2020</v>
       </c>
       <c r="M10" s="4" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="N10" s="4">
         <v>1</v>
@@ -5664,7 +5771,7 @@
         <v>14</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="R10" s="4" t="s">
         <v>67</v>
@@ -5684,10 +5791,10 @@
       <c r="X10" s="4"/>
       <c r="Y10" s="4"/>
       <c r="Z10" s="4" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AA10" s="4" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="AB10" s="4" t="s">
         <v>61</v>
@@ -5708,16 +5815,16 @@
         <v>31</v>
       </c>
       <c r="AH10" s="4" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="AI10" s="4" t="s">
         <v>52</v>
       </c>
       <c r="AJ10" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="AK10" s="12" t="s">
-        <v>104</v>
+        <v>113</v>
+      </c>
+      <c r="AK10" s="13" t="s">
+        <v>114</v>
       </c>
       <c r="AL10" s="4"/>
       <c r="AM10" s="4"/>
@@ -5985,35 +6092,35 @@
         <v>10</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="E11" s="4"/>
-      <c r="F11" s="8">
+      <c r="F11" s="9">
         <v>1</v>
       </c>
       <c r="G11" t="s">
-        <v>107</v>
-      </c>
-      <c r="H11" s="9">
+        <v>117</v>
+      </c>
+      <c r="H11" s="10">
         <v>0</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="J11" s="10" t="s">
-        <v>109</v>
+        <v>118</v>
+      </c>
+      <c r="J11" s="11" t="s">
+        <v>119</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="L11" s="4">
         <v>2021</v>
       </c>
       <c r="M11" s="4" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="N11" s="4">
         <v>1</v>
@@ -6026,7 +6133,7 @@
       </c>
       <c r="Q11" s="4"/>
       <c r="R11" s="4" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="S11" s="4">
         <v>12</v>
@@ -6040,18 +6147,18 @@
       <c r="V11" s="4">
         <v>7</v>
       </c>
-      <c r="W11" s="12" t="s">
-        <v>112</v>
+      <c r="W11" s="13" t="s">
+        <v>122</v>
       </c>
       <c r="X11" s="4"/>
       <c r="Y11" s="4" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="Z11" s="4" t="s">
         <v>70</v>
       </c>
       <c r="AA11" s="4" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="AB11" s="4" t="s">
         <v>61</v>
@@ -6073,16 +6180,16 @@
       </c>
       <c r="AH11" s="4"/>
       <c r="AI11" s="4" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="AJ11" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="AK11" s="12" t="s">
-        <v>117</v>
+        <v>126</v>
+      </c>
+      <c r="AK11" s="13" t="s">
+        <v>127</v>
       </c>
       <c r="AL11" s="4" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="AM11" s="4"/>
       <c r="AN11" s="4"/>
@@ -6349,25 +6456,25 @@
         <v>11</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="E12" s="7"/>
-      <c r="F12" s="8">
+        <v>130</v>
+      </c>
+      <c r="E12" s="8"/>
+      <c r="F12" s="9">
         <v>1</v>
       </c>
-      <c r="G12" s="9">
+      <c r="G12" s="10">
         <v>0</v>
       </c>
-      <c r="H12" s="9">
+      <c r="H12" s="10">
         <v>0</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="J12" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="J12" s="11" t="s">
         <v>42</v>
       </c>
       <c r="K12" s="4" t="s">
@@ -6377,7 +6484,7 @@
         <v>2020</v>
       </c>
       <c r="M12" s="4" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="N12" s="4">
         <v>2</v>
@@ -6433,16 +6540,16 @@
         <v>51</v>
       </c>
       <c r="AH12" s="4" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="AI12" s="4" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="AJ12" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="AK12" s="11" t="s">
-        <v>126</v>
+        <v>135</v>
+      </c>
+      <c r="AK12" s="12" t="s">
+        <v>136</v>
       </c>
       <c r="AL12" s="4"/>
       <c r="AM12" s="4"/>
@@ -6706,43 +6813,43 @@
     </row>
     <row r="13" ht="31" spans="1:296">
       <c r="A13" s="4" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="B13" s="4">
         <v>12</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="E13" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="E13" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="F13" s="8">
+      <c r="F13" s="9">
         <v>1</v>
       </c>
-      <c r="G13" s="9">
+      <c r="G13" s="10">
         <v>0</v>
       </c>
-      <c r="H13" s="9">
+      <c r="H13" s="10">
         <v>0</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="J13" s="10" t="s">
-        <v>131</v>
+        <v>140</v>
+      </c>
+      <c r="J13" s="11" t="s">
+        <v>141</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="L13" s="4">
         <v>2020</v>
       </c>
       <c r="M13" s="4" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="N13" s="4">
         <v>1</v>
@@ -6755,7 +6862,7 @@
       </c>
       <c r="Q13" s="4"/>
       <c r="R13" s="4" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="S13" s="4">
         <v>10</v>
@@ -6770,20 +6877,20 @@
         <v>47</v>
       </c>
       <c r="W13" s="4" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="X13" s="4"/>
       <c r="Y13" s="4" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="Z13" s="4" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="AA13" s="4" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="AB13" s="4" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="AC13" s="4">
         <v>26</v>
@@ -6806,13 +6913,13 @@
         <v>52</v>
       </c>
       <c r="AJ13" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="AK13" s="12" t="s">
-        <v>138</v>
-      </c>
-      <c r="AL13" s="11" t="s">
-        <v>139</v>
+        <v>147</v>
+      </c>
+      <c r="AK13" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="AL13" s="12" t="s">
+        <v>149</v>
       </c>
       <c r="AM13" s="4"/>
       <c r="AN13" s="4"/>
@@ -7079,33 +7186,33 @@
         <v>13</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="E14" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="E14" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="F14" s="8">
+      <c r="F14" s="9">
         <v>1</v>
       </c>
-      <c r="G14" s="9">
+      <c r="G14" s="10">
         <v>0</v>
       </c>
-      <c r="H14" s="9">
+      <c r="H14" s="10">
         <v>0</v>
       </c>
       <c r="I14" s="4"/>
-      <c r="J14" s="10"/>
+      <c r="J14" s="11"/>
       <c r="K14" s="4" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="L14" s="4">
         <v>2020</v>
       </c>
       <c r="M14" s="4" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="N14" s="4">
         <v>2</v>
@@ -7118,7 +7225,7 @@
       </c>
       <c r="Q14" s="4"/>
       <c r="R14" s="4" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="S14" s="4">
         <v>20</v>
@@ -7133,20 +7240,20 @@
         <v>2</v>
       </c>
       <c r="W14" s="4" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="X14" s="4"/>
       <c r="Y14" s="4" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="Z14" s="4" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="AA14" s="4" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="AB14" s="4" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="AC14" s="4">
         <v>26</v>
@@ -7165,19 +7272,19 @@
         <v>25</v>
       </c>
       <c r="AH14" s="4" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="AI14" s="4" t="s">
         <v>52</v>
       </c>
       <c r="AJ14" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="AK14" s="12" t="s">
-        <v>138</v>
-      </c>
-      <c r="AL14" s="10" t="s">
-        <v>139</v>
+        <v>147</v>
+      </c>
+      <c r="AK14" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="AL14" s="11" t="s">
+        <v>149</v>
       </c>
       <c r="AM14" s="4"/>
       <c r="AN14" s="4"/>
@@ -7444,37 +7551,37 @@
         <v>14</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="E15" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="E15" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="F15" s="8">
+      <c r="F15" s="9">
         <v>1</v>
       </c>
       <c r="G15" t="s">
-        <v>107</v>
-      </c>
-      <c r="H15" s="9">
+        <v>117</v>
+      </c>
+      <c r="H15" s="10">
         <v>0</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="J15" s="10" t="s">
-        <v>147</v>
+        <v>156</v>
+      </c>
+      <c r="J15" s="11" t="s">
+        <v>157</v>
       </c>
       <c r="K15" s="4" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="L15" s="4">
         <v>2019</v>
       </c>
       <c r="M15" s="4" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="N15" s="4">
         <v>1</v>
@@ -7486,10 +7593,10 @@
         <v>14</v>
       </c>
       <c r="Q15" s="4" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="R15" s="4" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="S15" s="4">
         <v>48</v>
@@ -7506,16 +7613,16 @@
       <c r="W15" s="4"/>
       <c r="X15" s="4"/>
       <c r="Y15" s="4" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="Z15" s="4" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="AA15" s="4" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="AB15" s="4" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="AC15" s="4">
         <v>103</v>
@@ -7534,19 +7641,19 @@
         <v>103</v>
       </c>
       <c r="AH15" s="4" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="AI15" s="4" t="s">
         <v>52</v>
       </c>
       <c r="AJ15" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="AK15" s="12" t="s">
-        <v>157</v>
+        <v>166</v>
+      </c>
+      <c r="AK15" s="13" t="s">
+        <v>167</v>
       </c>
       <c r="AL15" s="4" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="AM15" s="4"/>
       <c r="AN15" s="4"/>
@@ -7809,43 +7916,43 @@
     </row>
     <row r="16" ht="28" spans="1:296">
       <c r="A16" s="4" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="B16" s="4">
         <v>15</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="E16" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="E16" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="F16" s="8">
+      <c r="F16" s="9">
         <v>1</v>
       </c>
-      <c r="G16" s="9">
+      <c r="G16" s="10">
         <v>0</v>
       </c>
-      <c r="H16" s="8">
+      <c r="H16" s="9">
         <v>1</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="J16" s="10" t="s">
-        <v>163</v>
+        <v>172</v>
+      </c>
+      <c r="J16" s="11" t="s">
+        <v>173</v>
       </c>
       <c r="K16" s="4" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="L16" s="4">
         <v>2018</v>
       </c>
       <c r="M16" s="4" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="N16" s="4">
         <v>1</v>
@@ -7857,7 +7964,7 @@
         <v>14</v>
       </c>
       <c r="Q16" s="4" t="s">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="R16" s="4" t="s">
         <v>67</v>
@@ -7875,17 +7982,17 @@
         <v>4</v>
       </c>
       <c r="W16" s="4" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="X16" s="4"/>
       <c r="Y16" s="4" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="Z16" s="4" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="AA16" s="4" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="AB16" s="4" t="s">
         <v>61</v>
@@ -7908,16 +8015,16 @@
       </c>
       <c r="AH16" s="4"/>
       <c r="AI16" s="4" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="AJ16" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="AK16" s="13" t="s">
-        <v>170</v>
+        <v>179</v>
+      </c>
+      <c r="AK16" s="14" t="s">
+        <v>180</v>
       </c>
       <c r="AL16" s="4" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="AN16" s="4"/>
       <c r="AO16" s="4"/>
@@ -8179,39 +8286,39 @@
     </row>
     <row r="17" ht="28" spans="1:296">
       <c r="A17" s="4" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="B17" s="4">
         <v>16</v>
       </c>
       <c r="C17" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="D17" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="D17" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="E17" s="7" t="s">
+      <c r="E17" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="F17" s="8">
+      <c r="F17" s="9">
         <v>1</v>
       </c>
-      <c r="G17" s="9">
+      <c r="G17" s="10">
         <v>0</v>
       </c>
-      <c r="H17" s="8">
+      <c r="H17" s="9">
         <v>1</v>
       </c>
       <c r="I17" s="4"/>
-      <c r="J17" s="10"/>
+      <c r="J17" s="11"/>
       <c r="K17" s="4" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="L17" s="4">
         <v>2018</v>
       </c>
       <c r="M17" s="4" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="N17" s="4">
         <v>2</v>
@@ -8223,7 +8330,7 @@
         <v>14</v>
       </c>
       <c r="Q17" s="4" t="s">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="R17" s="4" t="s">
         <v>67</v>
@@ -8241,17 +8348,17 @@
         <v>4</v>
       </c>
       <c r="W17" s="4" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="X17" s="4"/>
       <c r="Y17" s="4" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="Z17" s="4" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="AA17" s="4" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="AB17" s="4" t="s">
         <v>61</v>
@@ -8274,16 +8381,16 @@
       </c>
       <c r="AH17" s="4"/>
       <c r="AI17" s="4" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="AJ17" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="AK17" s="14" t="s">
-        <v>170</v>
+        <v>179</v>
+      </c>
+      <c r="AK17" s="15" t="s">
+        <v>180</v>
       </c>
       <c r="AL17" s="4" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="AM17" s="4"/>
       <c r="AN17" s="4"/>
@@ -8546,37 +8653,37 @@
     </row>
     <row r="18" ht="15.5" spans="1:296">
       <c r="A18" s="4" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="B18" s="4">
         <v>17</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="E18" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="E18" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="F18" s="8">
+      <c r="F18" s="9">
         <v>1</v>
       </c>
-      <c r="G18" s="9">
+      <c r="G18" s="10">
         <v>0</v>
       </c>
-      <c r="H18" s="9">
+      <c r="H18" s="10">
         <v>0</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="J18" s="10" t="s">
-        <v>176</v>
+        <v>185</v>
+      </c>
+      <c r="J18" s="11" t="s">
+        <v>186</v>
       </c>
       <c r="K18" s="4" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="L18" s="4">
         <v>2021</v>
@@ -8594,7 +8701,7 @@
         <v>14</v>
       </c>
       <c r="Q18" s="4" t="s">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="R18" s="4" t="s">
         <v>67</v>
@@ -8612,7 +8719,7 @@
         <v>6</v>
       </c>
       <c r="W18" s="4" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="X18" s="4"/>
       <c r="Y18" s="4"/>
@@ -8620,7 +8727,7 @@
         <v>70</v>
       </c>
       <c r="AA18" s="4" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="AB18" s="4" t="s">
         <v>61</v>
@@ -8642,19 +8749,19 @@
         <v>25</v>
       </c>
       <c r="AH18" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="AI18" s="15" t="s">
+        <v>190</v>
+      </c>
+      <c r="AI18" s="16" t="s">
         <v>52</v>
       </c>
       <c r="AJ18" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="AK18" s="11" t="s">
-        <v>182</v>
+        <v>191</v>
+      </c>
+      <c r="AK18" s="12" t="s">
+        <v>192</v>
       </c>
       <c r="AL18" s="4" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="AM18" s="4"/>
       <c r="AN18" s="4"/>
@@ -8921,27 +9028,27 @@
         <v>18</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="E19" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="E19" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="F19" s="8">
+      <c r="F19" s="9">
         <v>1</v>
       </c>
-      <c r="G19" s="9">
+      <c r="G19" s="10">
         <v>0</v>
       </c>
-      <c r="H19" s="9">
+      <c r="H19" s="10">
         <v>0</v>
       </c>
       <c r="I19" s="4"/>
-      <c r="J19" s="10"/>
+      <c r="J19" s="11"/>
       <c r="K19" s="4" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="L19" s="4">
         <v>2021</v>
@@ -8959,7 +9066,7 @@
         <v>14</v>
       </c>
       <c r="Q19" s="4" t="s">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="R19" s="4" t="s">
         <v>67</v>
@@ -8983,7 +9090,7 @@
         <v>70</v>
       </c>
       <c r="AA19" s="4" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="AB19" s="4" t="s">
         <v>61</v>
@@ -9005,19 +9112,19 @@
         <v>25</v>
       </c>
       <c r="AH19" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="AI19" s="15" t="s">
+        <v>194</v>
+      </c>
+      <c r="AI19" s="16" t="s">
         <v>52</v>
       </c>
       <c r="AJ19" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="AK19" s="10" t="s">
-        <v>182</v>
+        <v>191</v>
+      </c>
+      <c r="AK19" s="11" t="s">
+        <v>192</v>
       </c>
       <c r="AL19" s="4" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="AM19" s="4"/>
       <c r="AN19" s="4"/>
@@ -9284,31 +9391,31 @@
         <v>19</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="E20" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="E20" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="F20" s="8">
+      <c r="F20" s="9">
         <v>1</v>
       </c>
-      <c r="G20" s="9">
+      <c r="G20" s="10">
         <v>0</v>
       </c>
-      <c r="H20" s="9">
+      <c r="H20" s="10">
         <v>0</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="J20" s="10" t="s">
-        <v>188</v>
+        <v>197</v>
+      </c>
+      <c r="J20" s="11" t="s">
+        <v>198</v>
       </c>
       <c r="K20" s="4" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="L20" s="4">
         <v>2021</v>
@@ -9324,7 +9431,7 @@
         <v>14</v>
       </c>
       <c r="Q20" s="4" t="s">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="R20" s="4" t="s">
         <v>67</v>
@@ -9344,16 +9451,16 @@
       <c r="W20" s="4"/>
       <c r="X20" s="4"/>
       <c r="Y20" s="4" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="Z20" s="4" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="AA20" s="4" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="AB20" s="4" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="AC20" s="4">
         <v>13</v>
@@ -9372,17 +9479,17 @@
         <v>13</v>
       </c>
       <c r="AH20" s="4"/>
-      <c r="AI20" s="15" t="s">
+      <c r="AI20" s="16" t="s">
         <v>52</v>
       </c>
       <c r="AJ20" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="AK20" s="11" t="s">
-        <v>194</v>
+        <v>203</v>
+      </c>
+      <c r="AK20" s="12" t="s">
+        <v>204</v>
       </c>
       <c r="AL20" s="4" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="AM20" s="4"/>
       <c r="AN20" s="4"/>
@@ -9649,27 +9756,27 @@
         <v>20</v>
       </c>
       <c r="C21" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="D21" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="D21" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="E21" s="7" t="s">
+      <c r="E21" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="F21" s="8">
+      <c r="F21" s="9">
         <v>1</v>
       </c>
-      <c r="G21" s="9">
+      <c r="G21" s="10">
         <v>0</v>
       </c>
-      <c r="H21" s="9">
+      <c r="H21" s="10">
         <v>0</v>
       </c>
       <c r="I21" s="4"/>
-      <c r="J21" s="10"/>
+      <c r="J21" s="11"/>
       <c r="K21" s="4" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="L21" s="4">
         <v>2021</v>
@@ -9681,11 +9788,11 @@
       <c r="O21" s="4">
         <v>2</v>
       </c>
-      <c r="P21" s="16" t="s">
-        <v>197</v>
+      <c r="P21" s="17" t="s">
+        <v>207</v>
       </c>
       <c r="Q21" s="4" t="s">
-        <v>198</v>
+        <v>208</v>
       </c>
       <c r="R21" s="4" t="s">
         <v>67</v>
@@ -9705,16 +9812,16 @@
       <c r="W21" s="4"/>
       <c r="X21" s="4"/>
       <c r="Y21" s="4" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="Z21" s="4" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="AA21" s="4" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="AB21" s="4" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="AC21" s="4">
         <v>27</v>
@@ -9733,17 +9840,17 @@
         <v>27</v>
       </c>
       <c r="AH21" s="4"/>
-      <c r="AI21" s="15" t="s">
+      <c r="AI21" s="16" t="s">
         <v>52</v>
       </c>
       <c r="AJ21" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="AK21" s="10" t="s">
-        <v>194</v>
+        <v>203</v>
+      </c>
+      <c r="AK21" s="11" t="s">
+        <v>204</v>
       </c>
       <c r="AL21" s="4" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="AM21" s="4"/>
       <c r="AN21" s="4"/>
@@ -10010,27 +10117,27 @@
         <v>21</v>
       </c>
       <c r="C22" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="F22" s="9">
+        <v>1</v>
+      </c>
+      <c r="G22" s="10">
+        <v>0</v>
+      </c>
+      <c r="H22" s="10">
+        <v>0</v>
+      </c>
+      <c r="I22" s="4"/>
+      <c r="J22" s="11"/>
+      <c r="K22" s="4" t="s">
         <v>199</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="E22" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="F22" s="8">
-        <v>1</v>
-      </c>
-      <c r="G22" s="9">
-        <v>0</v>
-      </c>
-      <c r="H22" s="9">
-        <v>0</v>
-      </c>
-      <c r="I22" s="4"/>
-      <c r="J22" s="10"/>
-      <c r="K22" s="4" t="s">
-        <v>189</v>
       </c>
       <c r="L22" s="4">
         <v>2021</v>
@@ -10046,7 +10153,7 @@
         <v>14</v>
       </c>
       <c r="Q22" s="4" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="R22" s="4" t="s">
         <v>67</v>
@@ -10066,16 +10173,16 @@
       <c r="W22" s="4"/>
       <c r="X22" s="4"/>
       <c r="Y22" s="4" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="Z22" s="4" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="AA22" s="4" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="AB22" s="4" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="AC22" s="4">
         <v>27</v>
@@ -10094,17 +10201,17 @@
         <v>27</v>
       </c>
       <c r="AH22" s="4"/>
-      <c r="AI22" s="15" t="s">
+      <c r="AI22" s="16" t="s">
         <v>52</v>
       </c>
       <c r="AJ22" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="AK22" s="10" t="s">
-        <v>194</v>
+        <v>203</v>
+      </c>
+      <c r="AK22" s="11" t="s">
+        <v>204</v>
       </c>
       <c r="AL22" s="4" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="AM22" s="4"/>
       <c r="AN22" s="4"/>
@@ -10371,27 +10478,27 @@
         <v>22</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="E23" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="E23" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="F23" s="8">
+      <c r="F23" s="9">
         <v>1</v>
       </c>
-      <c r="G23" s="9">
+      <c r="G23" s="10">
         <v>0</v>
       </c>
-      <c r="H23" s="9">
+      <c r="H23" s="10">
         <v>0</v>
       </c>
       <c r="I23" s="4"/>
-      <c r="J23" s="10"/>
+      <c r="J23" s="11"/>
       <c r="K23" s="4" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="L23" s="4">
         <v>2021</v>
@@ -10407,7 +10514,7 @@
         <v>14</v>
       </c>
       <c r="Q23" s="4" t="s">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="R23" s="4" t="s">
         <v>67</v>
@@ -10427,16 +10534,16 @@
       <c r="W23" s="4"/>
       <c r="X23" s="4"/>
       <c r="Y23" s="4" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="Z23" s="4" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="AA23" s="4" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="AB23" s="4" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="AC23" s="4">
         <v>26</v>
@@ -10455,17 +10562,17 @@
         <v>25</v>
       </c>
       <c r="AH23" s="4"/>
-      <c r="AI23" s="15" t="s">
+      <c r="AI23" s="16" t="s">
         <v>52</v>
       </c>
       <c r="AJ23" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="AK23" s="10" t="s">
-        <v>194</v>
+        <v>203</v>
+      </c>
+      <c r="AK23" s="11" t="s">
+        <v>204</v>
       </c>
       <c r="AL23" s="4" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="AM23" s="4"/>
       <c r="AN23" s="4"/>
@@ -10732,35 +10839,35 @@
         <v>23</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="E24" s="4"/>
-      <c r="F24" s="8">
+      <c r="F24" s="9">
         <v>1</v>
       </c>
-      <c r="G24" s="9">
+      <c r="G24" s="10">
         <v>0</v>
       </c>
-      <c r="H24" s="9">
+      <c r="H24" s="10">
         <v>0</v>
       </c>
       <c r="I24" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="J24" s="10" t="s">
-        <v>204</v>
+        <v>213</v>
+      </c>
+      <c r="J24" s="11" t="s">
+        <v>214</v>
       </c>
       <c r="K24" s="4" t="s">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="L24" s="4">
         <v>2020</v>
       </c>
       <c r="M24" s="4" t="s">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="N24" s="4">
         <v>1</v>
@@ -10790,16 +10897,16 @@
       <c r="W24" s="4"/>
       <c r="X24" s="4"/>
       <c r="Y24" s="4" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="Z24" s="4" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="AA24" s="4" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="AB24" s="4" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="AC24" s="4">
         <v>38</v>
@@ -10818,16 +10925,16 @@
         <v>34</v>
       </c>
       <c r="AH24" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="AI24" s="15" t="s">
+        <v>218</v>
+      </c>
+      <c r="AI24" s="16" t="s">
         <v>52</v>
       </c>
       <c r="AJ24" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="AK24" s="10" t="s">
-        <v>210</v>
+        <v>219</v>
+      </c>
+      <c r="AK24" s="11" t="s">
+        <v>220</v>
       </c>
       <c r="AL24" s="4"/>
       <c r="AM24" s="4"/>
@@ -11095,31 +11202,31 @@
         <v>24</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="E25" s="4"/>
-      <c r="F25" s="8">
+      <c r="F25" s="9">
         <v>1</v>
       </c>
-      <c r="G25" s="9">
+      <c r="G25" s="10">
         <v>0</v>
       </c>
-      <c r="H25" s="9">
+      <c r="H25" s="10">
         <v>0</v>
       </c>
       <c r="I25" s="4"/>
-      <c r="J25" s="10"/>
+      <c r="J25" s="11"/>
       <c r="K25" s="4" t="s">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="L25" s="4">
         <v>2020</v>
       </c>
       <c r="M25" s="4" t="s">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="N25" s="4">
         <v>2</v>
@@ -11149,16 +11256,16 @@
       <c r="W25" s="4"/>
       <c r="X25" s="4"/>
       <c r="Y25" s="4" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="Z25" s="4" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="AA25" s="4" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="AB25" s="4" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="AC25" s="4">
         <v>33</v>
@@ -11177,16 +11284,16 @@
         <v>31</v>
       </c>
       <c r="AH25" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="AI25" s="15" t="s">
+        <v>222</v>
+      </c>
+      <c r="AI25" s="16" t="s">
         <v>52</v>
       </c>
       <c r="AJ25" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="AK25" s="10" t="s">
-        <v>210</v>
+        <v>219</v>
+      </c>
+      <c r="AK25" s="11" t="s">
+        <v>220</v>
       </c>
       <c r="AL25" s="4"/>
       <c r="AM25" s="4"/>
@@ -11454,31 +11561,31 @@
         <v>25</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="E26" s="4"/>
-      <c r="F26" s="8">
+      <c r="F26" s="9">
         <v>1</v>
       </c>
-      <c r="G26" s="9">
+      <c r="G26" s="10">
         <v>0</v>
       </c>
-      <c r="H26" s="9">
+      <c r="H26" s="10">
         <v>0</v>
       </c>
       <c r="I26" s="4"/>
-      <c r="J26" s="10"/>
+      <c r="J26" s="11"/>
       <c r="K26" s="4" t="s">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="L26" s="4">
         <v>2020</v>
       </c>
       <c r="M26" s="4" t="s">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="N26" s="4">
         <v>3</v>
@@ -11508,16 +11615,16 @@
       <c r="W26" s="4"/>
       <c r="X26" s="4"/>
       <c r="Y26" s="4" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="Z26" s="4" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="AA26" s="4" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="AB26" s="4" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="AC26" s="4">
         <v>36</v>
@@ -11536,16 +11643,16 @@
         <v>35</v>
       </c>
       <c r="AH26" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="AI26" s="15" t="s">
+        <v>224</v>
+      </c>
+      <c r="AI26" s="16" t="s">
         <v>52</v>
       </c>
       <c r="AJ26" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="AK26" s="10" t="s">
-        <v>210</v>
+        <v>219</v>
+      </c>
+      <c r="AK26" s="11" t="s">
+        <v>220</v>
       </c>
       <c r="AL26" s="4"/>
       <c r="AM26" s="4"/>
@@ -11813,37 +11920,37 @@
         <v>26</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>216</v>
-      </c>
-      <c r="E27" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="E27" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="F27" s="8">
+      <c r="F27" s="9">
         <v>1</v>
       </c>
-      <c r="G27" s="9">
+      <c r="G27" s="10">
         <v>0</v>
       </c>
-      <c r="H27" s="9">
+      <c r="H27" s="10">
         <v>0</v>
       </c>
       <c r="I27" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="J27" s="10" t="s">
-        <v>218</v>
+        <v>227</v>
+      </c>
+      <c r="J27" s="11" t="s">
+        <v>228</v>
       </c>
       <c r="K27" s="4" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="L27" s="4">
         <v>2022</v>
       </c>
       <c r="M27" s="4" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="N27" s="4">
         <v>1</v>
@@ -11855,7 +11962,7 @@
         <v>14</v>
       </c>
       <c r="Q27" s="4" t="s">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="R27" s="4"/>
       <c r="S27" s="4">
@@ -11877,7 +11984,7 @@
         <v>70</v>
       </c>
       <c r="AA27" s="4" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="AB27" s="4" t="s">
         <v>61</v>
@@ -11899,16 +12006,16 @@
         <v>20</v>
       </c>
       <c r="AH27" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="AI27" s="15" t="s">
+        <v>232</v>
+      </c>
+      <c r="AI27" s="16" t="s">
         <v>52</v>
       </c>
       <c r="AJ27" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="AK27" s="11" t="s">
-        <v>224</v>
+        <v>233</v>
+      </c>
+      <c r="AK27" s="12" t="s">
+        <v>234</v>
       </c>
       <c r="AL27" s="4"/>
       <c r="AM27" s="4"/>
@@ -12176,33 +12283,33 @@
         <v>27</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>216</v>
-      </c>
-      <c r="E28" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="E28" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="F28" s="8">
+      <c r="F28" s="9">
         <v>1</v>
       </c>
-      <c r="G28" s="9">
+      <c r="G28" s="10">
         <v>0</v>
       </c>
-      <c r="H28" s="9">
+      <c r="H28" s="10">
         <v>0</v>
       </c>
       <c r="I28" s="4"/>
-      <c r="J28" s="10"/>
+      <c r="J28" s="11"/>
       <c r="K28" s="4" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="L28" s="4">
         <v>2022</v>
       </c>
       <c r="M28" s="4" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="N28" s="4">
         <v>2</v>
@@ -12214,7 +12321,7 @@
         <v>14</v>
       </c>
       <c r="Q28" s="4" t="s">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="R28" s="4"/>
       <c r="S28" s="4">
@@ -12230,7 +12337,7 @@
         <v>2</v>
       </c>
       <c r="W28" s="4" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="X28" s="4"/>
       <c r="Y28" s="4"/>
@@ -12238,7 +12345,7 @@
         <v>70</v>
       </c>
       <c r="AA28" s="4" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="AB28" s="4" t="s">
         <v>61</v>
@@ -12260,16 +12367,16 @@
         <v>24</v>
       </c>
       <c r="AH28" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="AI28" s="15" t="s">
+        <v>237</v>
+      </c>
+      <c r="AI28" s="16" t="s">
         <v>52</v>
       </c>
       <c r="AJ28" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="AK28" s="10" t="s">
-        <v>224</v>
+        <v>233</v>
+      </c>
+      <c r="AK28" s="11" t="s">
+        <v>234</v>
       </c>
       <c r="AL28" s="4"/>
       <c r="AM28" s="4"/>
@@ -12537,33 +12644,33 @@
         <v>28</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>216</v>
-      </c>
-      <c r="E29" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="E29" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="F29" s="8">
+      <c r="F29" s="9">
         <v>1</v>
       </c>
-      <c r="G29" s="9">
+      <c r="G29" s="10">
         <v>0</v>
       </c>
-      <c r="H29" s="9">
+      <c r="H29" s="10">
         <v>0</v>
       </c>
       <c r="I29" s="4"/>
-      <c r="J29" s="10"/>
+      <c r="J29" s="11"/>
       <c r="K29" s="4" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="L29" s="4">
         <v>2022</v>
       </c>
       <c r="M29" s="4" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="N29" s="4">
         <v>3</v>
@@ -12575,7 +12682,7 @@
         <v>14</v>
       </c>
       <c r="Q29" s="4" t="s">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="R29" s="4"/>
       <c r="S29" s="4">
@@ -12591,7 +12698,7 @@
         <v>2</v>
       </c>
       <c r="W29" s="4" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="X29" s="4"/>
       <c r="Y29" s="4"/>
@@ -12599,7 +12706,7 @@
         <v>70</v>
       </c>
       <c r="AA29" s="4" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="AB29" s="4" t="s">
         <v>61</v>
@@ -12621,16 +12728,16 @@
         <v>25</v>
       </c>
       <c r="AH29" s="4" t="s">
-        <v>230</v>
-      </c>
-      <c r="AI29" s="15" t="s">
+        <v>240</v>
+      </c>
+      <c r="AI29" s="16" t="s">
         <v>52</v>
       </c>
       <c r="AJ29" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="AK29" s="10" t="s">
-        <v>224</v>
+        <v>233</v>
+      </c>
+      <c r="AK29" s="11" t="s">
+        <v>234</v>
       </c>
       <c r="AL29" s="4"/>
       <c r="AM29" s="4"/>
@@ -12898,37 +13005,37 @@
         <v>29</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="E30" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="E30" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="F30" s="8">
+      <c r="F30" s="9">
         <v>1</v>
       </c>
-      <c r="G30" s="9">
+      <c r="G30" s="10">
         <v>0</v>
       </c>
-      <c r="H30" s="9">
+      <c r="H30" s="10">
         <v>0</v>
       </c>
       <c r="I30" s="4" t="s">
-        <v>233</v>
-      </c>
-      <c r="J30" s="10" t="s">
-        <v>234</v>
+        <v>243</v>
+      </c>
+      <c r="J30" s="11" t="s">
+        <v>244</v>
       </c>
       <c r="K30" s="4" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="L30" s="4">
         <v>2021</v>
       </c>
       <c r="M30" s="4" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="N30" s="4">
         <v>1</v>
@@ -12940,7 +13047,7 @@
         <v>14</v>
       </c>
       <c r="Q30" s="4" t="s">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="R30" s="4" t="s">
         <v>67</v>
@@ -12957,21 +13064,21 @@
       <c r="V30" s="4">
         <v>3</v>
       </c>
-      <c r="W30" s="17" t="s">
-        <v>237</v>
+      <c r="W30" s="18" t="s">
+        <v>247</v>
       </c>
       <c r="X30" s="4"/>
       <c r="Y30" s="4" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="Z30" s="4" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="AA30" s="4" t="s">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="AB30" s="4" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="AC30" s="4">
         <v>105</v>
@@ -12990,14 +13097,14 @@
         <v>105</v>
       </c>
       <c r="AH30" s="4"/>
-      <c r="AI30" s="15" t="s">
+      <c r="AI30" s="16" t="s">
         <v>52</v>
       </c>
       <c r="AJ30" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="AK30" s="12" t="s">
-        <v>240</v>
+        <v>249</v>
+      </c>
+      <c r="AK30" s="13" t="s">
+        <v>250</v>
       </c>
       <c r="AL30" s="4"/>
       <c r="AM30" s="4"/>
@@ -13261,43 +13368,43 @@
     </row>
     <row r="31" ht="17" customHeight="1" spans="1:296">
       <c r="A31" s="4" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="B31" s="4">
         <v>30</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="E31" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="E31" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="F31" s="8">
+      <c r="F31" s="9">
         <v>1</v>
       </c>
       <c r="G31" t="s">
-        <v>107</v>
-      </c>
-      <c r="H31" s="9">
+        <v>117</v>
+      </c>
+      <c r="H31" s="10">
         <v>0</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="J31" s="10" t="s">
-        <v>244</v>
+        <v>253</v>
+      </c>
+      <c r="J31" s="11" t="s">
+        <v>254</v>
       </c>
       <c r="K31" s="4" t="s">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="L31" s="4">
         <v>2023</v>
       </c>
       <c r="M31" s="4" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="N31" s="4">
         <v>1</v>
@@ -13327,13 +13434,13 @@
       <c r="W31" s="4"/>
       <c r="X31" s="4"/>
       <c r="Y31" s="4" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="Z31" s="4" t="s">
         <v>70</v>
       </c>
       <c r="AA31" s="4" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="AB31" s="4" t="s">
         <v>61</v>
@@ -13356,16 +13463,16 @@
       </c>
       <c r="AH31" s="4"/>
       <c r="AI31" s="4" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="AJ31" s="4" t="s">
-        <v>249</v>
-      </c>
-      <c r="AK31" s="10" t="s">
-        <v>250</v>
+        <v>259</v>
+      </c>
+      <c r="AK31" s="11" t="s">
+        <v>260</v>
       </c>
       <c r="AL31" s="4" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="AM31" s="4"/>
       <c r="AN31" s="4"/>
@@ -13628,37 +13735,37 @@
     </row>
     <row r="32" ht="15.5" spans="1:296">
       <c r="A32" s="4" t="s">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="B32" s="4">
         <v>31</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>254</v>
-      </c>
-      <c r="E32" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="E32" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="F32" s="8">
+      <c r="F32" s="9">
         <v>1</v>
       </c>
-      <c r="G32" s="9">
+      <c r="G32" s="10">
         <v>0</v>
       </c>
-      <c r="H32" s="9">
+      <c r="H32" s="10">
         <v>0</v>
       </c>
       <c r="I32" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="J32" s="10" t="s">
-        <v>82</v>
+        <v>92</v>
+      </c>
+      <c r="J32" s="11" t="s">
+        <v>93</v>
       </c>
       <c r="K32" s="4" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="L32" s="4">
         <v>2023</v>
@@ -13668,7 +13775,7 @@
         <v>1</v>
       </c>
       <c r="O32" s="4" t="s">
-        <v>255</v>
+        <v>265</v>
       </c>
       <c r="P32" s="4" t="s">
         <v>14</v>
@@ -13690,24 +13797,24 @@
         <v>2</v>
       </c>
       <c r="W32" s="4" t="s">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="X32" s="4"/>
       <c r="Y32" s="4"/>
       <c r="Z32" s="4" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="AA32" s="4" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="AB32" s="4" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="AC32" s="4">
         <v>23</v>
       </c>
       <c r="AD32" s="1" t="s">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="AE32" s="1"/>
       <c r="AF32" s="4">
@@ -13718,19 +13825,19 @@
         <v>22</v>
       </c>
       <c r="AH32" s="4" t="s">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c r="AI32" s="4" t="s">
         <v>52</v>
       </c>
       <c r="AJ32" s="4" t="s">
-        <v>259</v>
-      </c>
-      <c r="AK32" s="11" t="s">
-        <v>260</v>
+        <v>269</v>
+      </c>
+      <c r="AK32" s="12" t="s">
+        <v>270</v>
       </c>
       <c r="AL32" s="4" t="s">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="AM32" s="4"/>
       <c r="AN32" s="4"/>
@@ -13993,33 +14100,33 @@
     </row>
     <row r="33" ht="16" customHeight="1" spans="1:296">
       <c r="A33" s="4" t="s">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="B33" s="4">
         <v>32</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>264</v>
-      </c>
-      <c r="E33" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="E33" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="F33" s="8">
+      <c r="F33" s="9">
         <v>1</v>
       </c>
-      <c r="G33" s="9">
+      <c r="G33" s="10">
         <v>0</v>
       </c>
-      <c r="H33" s="9">
+      <c r="H33" s="10">
         <v>0</v>
       </c>
       <c r="I33" s="4"/>
-      <c r="J33" s="10"/>
+      <c r="J33" s="11"/>
       <c r="K33" s="4" t="s">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="L33" s="4">
         <v>2014</v>
@@ -14035,7 +14142,7 @@
         <v>14</v>
       </c>
       <c r="Q33" s="4" t="s">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="R33" s="4" t="s">
         <v>67</v>
@@ -14050,13 +14157,13 @@
       <c r="X33" s="4"/>
       <c r="Y33" s="4"/>
       <c r="Z33" s="4" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="AA33" s="4" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="AB33" s="4" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="AC33" s="4">
         <v>24</v>
@@ -14073,7 +14180,7 @@
         <v>52</v>
       </c>
       <c r="AJ33" s="4" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="AK33" s="4"/>
       <c r="AL33" s="4"/>
@@ -14338,33 +14445,33 @@
     </row>
     <row r="34" ht="15.5" spans="1:296">
       <c r="A34" s="4" t="s">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="B34" s="4">
         <v>33</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>267</v>
+        <v>277</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>268</v>
-      </c>
-      <c r="E34" s="7" t="s">
+        <v>278</v>
+      </c>
+      <c r="E34" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="F34" s="8">
+      <c r="F34" s="9">
         <v>1</v>
       </c>
-      <c r="G34" s="9">
+      <c r="G34" s="10">
         <v>0</v>
       </c>
-      <c r="H34" s="9">
+      <c r="H34" s="10">
         <v>0</v>
       </c>
       <c r="I34" s="4"/>
-      <c r="J34" s="10"/>
+      <c r="J34" s="11"/>
       <c r="K34" s="4" t="s">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="L34" s="4">
         <v>2015</v>
@@ -14380,7 +14487,7 @@
         <v>14</v>
       </c>
       <c r="Q34" s="4" t="s">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="R34" s="4" t="s">
         <v>67</v>
@@ -14395,13 +14502,13 @@
       <c r="X34" s="4"/>
       <c r="Y34" s="4"/>
       <c r="Z34" s="4" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="AA34" s="4" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="AB34" s="4" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="AC34" s="4">
         <v>20</v>
@@ -14418,7 +14525,7 @@
         <v>52</v>
       </c>
       <c r="AJ34" s="4" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="AK34" s="4"/>
       <c r="AL34" s="4"/>
@@ -14683,33 +14790,33 @@
     </row>
     <row r="35" ht="15.5" spans="1:296">
       <c r="A35" s="4" t="s">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="B35" s="4">
         <v>34</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>268</v>
-      </c>
-      <c r="E35" s="7" t="s">
+        <v>278</v>
+      </c>
+      <c r="E35" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="F35" s="8">
+      <c r="F35" s="9">
         <v>1</v>
       </c>
-      <c r="G35" s="9">
+      <c r="G35" s="10">
         <v>0</v>
       </c>
-      <c r="H35" s="9">
+      <c r="H35" s="10">
         <v>0</v>
       </c>
       <c r="I35" s="4"/>
-      <c r="J35" s="10"/>
+      <c r="J35" s="11"/>
       <c r="K35" s="4" t="s">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="L35" s="4">
         <v>2015</v>
@@ -14725,7 +14832,7 @@
         <v>14</v>
       </c>
       <c r="Q35" s="4" t="s">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="R35" s="4" t="s">
         <v>67</v>
@@ -14740,13 +14847,13 @@
       <c r="X35" s="4"/>
       <c r="Y35" s="4"/>
       <c r="Z35" s="4" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="AA35" s="4" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="AB35" s="4" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="AC35" s="4">
         <v>21</v>
@@ -14760,10 +14867,10 @@
       </c>
       <c r="AH35" s="4"/>
       <c r="AI35" s="4" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="AJ35" s="4" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="AK35" s="4"/>
       <c r="AL35" s="4"/>
@@ -15028,39 +15135,39 @@
     </row>
     <row r="36" ht="15.5" spans="1:296">
       <c r="A36" s="4" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="B36" s="4">
         <v>35</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>273</v>
-      </c>
-      <c r="E36" s="7" t="s">
+        <v>283</v>
+      </c>
+      <c r="E36" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="F36" s="8">
+      <c r="F36" s="9">
         <v>1</v>
       </c>
-      <c r="G36" s="9">
+      <c r="G36" s="10">
         <v>0</v>
       </c>
-      <c r="H36" s="9">
+      <c r="H36" s="10">
         <v>0</v>
       </c>
       <c r="I36" s="4"/>
-      <c r="J36" s="10"/>
+      <c r="J36" s="11"/>
       <c r="K36" s="4" t="s">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="L36" s="4">
         <v>2014</v>
       </c>
       <c r="M36" s="4" t="s">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="N36" s="4">
         <v>1</v>
@@ -15072,7 +15179,7 @@
         <v>14</v>
       </c>
       <c r="Q36" s="4" t="s">
-        <v>276</v>
+        <v>286</v>
       </c>
       <c r="R36" s="4" t="s">
         <v>67</v>
@@ -15084,18 +15191,18 @@
       </c>
       <c r="V36" s="4"/>
       <c r="W36" s="4" t="s">
-        <v>277</v>
+        <v>287</v>
       </c>
       <c r="X36" s="4"/>
       <c r="Y36" s="4"/>
       <c r="Z36" s="4" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="AA36" s="4" t="s">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="AB36" s="4" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="AC36" s="4">
         <v>24</v>
@@ -15112,7 +15219,7 @@
         <v>52</v>
       </c>
       <c r="AJ36" s="4" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="AK36" s="4"/>
       <c r="AL36" s="4"/>
@@ -15377,39 +15484,39 @@
     </row>
     <row r="37" ht="15.5" spans="1:296">
       <c r="A37" s="4" t="s">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="B37" s="4">
         <v>36</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>281</v>
+        <v>291</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>273</v>
-      </c>
-      <c r="E37" s="7" t="s">
+        <v>283</v>
+      </c>
+      <c r="E37" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="F37" s="8">
+      <c r="F37" s="9">
         <v>1</v>
       </c>
-      <c r="G37" s="9">
+      <c r="G37" s="10">
         <v>0</v>
       </c>
-      <c r="H37" s="9">
+      <c r="H37" s="10">
         <v>0</v>
       </c>
       <c r="I37" s="4"/>
-      <c r="J37" s="10"/>
+      <c r="J37" s="11"/>
       <c r="K37" s="4" t="s">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="L37" s="4">
         <v>2014</v>
       </c>
       <c r="M37" s="4" t="s">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="N37" s="4">
         <v>2</v>
@@ -15421,7 +15528,7 @@
         <v>14</v>
       </c>
       <c r="Q37" s="4" t="s">
-        <v>276</v>
+        <v>286</v>
       </c>
       <c r="R37" s="4" t="s">
         <v>67</v>
@@ -15433,18 +15540,18 @@
       </c>
       <c r="V37" s="4"/>
       <c r="W37" s="4" t="s">
-        <v>282</v>
+        <v>292</v>
       </c>
       <c r="X37" s="4"/>
       <c r="Y37" s="4"/>
       <c r="Z37" s="4" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="AA37" s="4" t="s">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="AB37" s="4" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="AC37" s="4">
         <v>18</v>
@@ -15461,7 +15568,7 @@
         <v>52</v>
       </c>
       <c r="AJ37" s="4" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="AK37" s="4"/>
       <c r="AL37" s="4"/>
@@ -15726,39 +15833,39 @@
     </row>
     <row r="38" ht="15.5" spans="1:296">
       <c r="A38" s="4" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="B38" s="4">
         <v>37</v>
       </c>
       <c r="C38" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="E38" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="F38" s="9">
+        <v>1</v>
+      </c>
+      <c r="G38" s="10">
+        <v>0</v>
+      </c>
+      <c r="H38" s="10">
+        <v>0</v>
+      </c>
+      <c r="I38" s="4"/>
+      <c r="J38" s="11"/>
+      <c r="K38" s="4" t="s">
         <v>284</v>
-      </c>
-      <c r="D38" s="4" t="s">
-        <v>273</v>
-      </c>
-      <c r="E38" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="F38" s="8">
-        <v>1</v>
-      </c>
-      <c r="G38" s="9">
-        <v>0</v>
-      </c>
-      <c r="H38" s="9">
-        <v>0</v>
-      </c>
-      <c r="I38" s="4"/>
-      <c r="J38" s="10"/>
-      <c r="K38" s="4" t="s">
-        <v>274</v>
       </c>
       <c r="L38" s="4">
         <v>2014</v>
       </c>
       <c r="M38" s="4" t="s">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="N38" s="4">
         <v>3</v>
@@ -15770,7 +15877,7 @@
         <v>14</v>
       </c>
       <c r="Q38" s="4" t="s">
-        <v>276</v>
+        <v>286</v>
       </c>
       <c r="R38" s="4" t="s">
         <v>67</v>
@@ -15782,18 +15889,18 @@
       </c>
       <c r="V38" s="4"/>
       <c r="W38" s="4" t="s">
-        <v>285</v>
+        <v>295</v>
       </c>
       <c r="X38" s="4"/>
       <c r="Y38" s="4"/>
       <c r="Z38" s="4" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="AA38" s="4" t="s">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="AB38" s="4" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="AC38" s="4">
         <v>22</v>
@@ -15810,7 +15917,7 @@
         <v>52</v>
       </c>
       <c r="AJ38" s="4" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="AK38" s="4"/>
       <c r="AL38" s="4"/>
@@ -16075,39 +16182,39 @@
     </row>
     <row r="39" ht="15.5" spans="1:296">
       <c r="A39" s="4" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="B39" s="4">
         <v>38</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>273</v>
-      </c>
-      <c r="E39" s="7" t="s">
+        <v>283</v>
+      </c>
+      <c r="E39" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="F39" s="8">
+      <c r="F39" s="9">
         <v>1</v>
       </c>
-      <c r="G39" s="9">
+      <c r="G39" s="10">
         <v>0</v>
       </c>
-      <c r="H39" s="9">
+      <c r="H39" s="10">
         <v>0</v>
       </c>
       <c r="I39" s="4"/>
-      <c r="J39" s="10"/>
+      <c r="J39" s="11"/>
       <c r="K39" s="4" t="s">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="L39" s="4">
         <v>2014</v>
       </c>
       <c r="M39" s="4" t="s">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="N39" s="4">
         <v>4</v>
@@ -16119,7 +16226,7 @@
         <v>14</v>
       </c>
       <c r="Q39" s="4" t="s">
-        <v>276</v>
+        <v>286</v>
       </c>
       <c r="R39" s="4" t="s">
         <v>67</v>
@@ -16131,18 +16238,18 @@
       </c>
       <c r="V39" s="4"/>
       <c r="W39" s="4" t="s">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="X39" s="4"/>
       <c r="Y39" s="4"/>
       <c r="Z39" s="4" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="AA39" s="4" t="s">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="AB39" s="4" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="AC39" s="4">
         <v>20</v>
@@ -16159,7 +16266,7 @@
         <v>52</v>
       </c>
       <c r="AJ39" s="4" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="AK39" s="4"/>
       <c r="AM39" s="4"/>
@@ -16427,37 +16534,37 @@
         <v>39</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>289</v>
+        <v>299</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="E40" s="7" t="s">
+        <v>300</v>
+      </c>
+      <c r="E40" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="F40" s="8">
+      <c r="F40" s="9">
         <v>1</v>
       </c>
-      <c r="G40" s="18">
+      <c r="G40" s="19">
         <v>0</v>
       </c>
-      <c r="H40" s="8">
+      <c r="H40" s="9">
         <v>1</v>
       </c>
       <c r="I40" s="4" t="s">
-        <v>291</v>
-      </c>
-      <c r="J40" s="10" t="s">
-        <v>292</v>
+        <v>301</v>
+      </c>
+      <c r="J40" s="11" t="s">
+        <v>302</v>
       </c>
       <c r="K40" s="4" t="s">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="L40" s="4">
         <v>2023</v>
       </c>
       <c r="M40" s="4" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="N40" s="4">
         <v>1</v>
@@ -16485,16 +16592,16 @@
       <c r="W40" s="4"/>
       <c r="X40" s="4"/>
       <c r="Y40" s="4" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="Z40" s="4" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="AA40" s="4" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="AB40" s="4" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="AC40" s="4">
         <v>40</v>
@@ -16513,19 +16620,19 @@
         <v>37</v>
       </c>
       <c r="AH40" s="4" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="AI40" s="4" t="s">
         <v>52</v>
       </c>
       <c r="AJ40" s="4" t="s">
-        <v>296</v>
-      </c>
-      <c r="AK40" s="13" t="s">
-        <v>297</v>
+        <v>306</v>
+      </c>
+      <c r="AK40" s="14" t="s">
+        <v>307</v>
       </c>
       <c r="AL40" s="4" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="AM40" s="4"/>
       <c r="AN40" s="4"/>
@@ -16792,37 +16899,37 @@
         <v>40</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>298</v>
+        <v>308</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>299</v>
-      </c>
-      <c r="E41" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="E41" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="F41" s="8">
+      <c r="F41" s="9">
         <v>1</v>
       </c>
-      <c r="G41" s="8">
+      <c r="G41" s="9">
         <v>1</v>
       </c>
-      <c r="H41" s="18">
+      <c r="H41" s="19">
         <v>0</v>
       </c>
       <c r="I41" s="4" t="s">
-        <v>300</v>
-      </c>
-      <c r="J41" s="10" t="s">
-        <v>301</v>
+        <v>310</v>
+      </c>
+      <c r="J41" s="11" t="s">
+        <v>311</v>
       </c>
       <c r="K41" s="4" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="L41" s="4">
         <v>2023</v>
       </c>
       <c r="M41" s="4" t="s">
-        <v>303</v>
+        <v>313</v>
       </c>
       <c r="N41" s="4">
         <v>1</v>
@@ -16834,7 +16941,7 @@
         <v>14</v>
       </c>
       <c r="Q41" s="4" t="s">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="R41" s="4" t="s">
         <v>67</v>
@@ -16858,7 +16965,7 @@
         <v>70</v>
       </c>
       <c r="AA41" s="4" t="s">
-        <v>304</v>
+        <v>314</v>
       </c>
       <c r="AB41" s="4" t="s">
         <v>61</v>
@@ -16881,16 +16988,16 @@
       </c>
       <c r="AH41" s="4"/>
       <c r="AI41" s="4" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="AJ41" s="4" t="s">
-        <v>305</v>
-      </c>
-      <c r="AK41" s="11" t="s">
-        <v>306</v>
+        <v>315</v>
+      </c>
+      <c r="AK41" s="12" t="s">
+        <v>316</v>
       </c>
       <c r="AL41" s="4" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="AM41" s="4"/>
       <c r="AN41" s="4"/>
@@ -17157,37 +17264,37 @@
         <v>41</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>308</v>
-      </c>
-      <c r="E42" s="7" t="s">
+        <v>318</v>
+      </c>
+      <c r="E42" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="F42" s="8">
+      <c r="F42" s="9">
         <v>1</v>
       </c>
-      <c r="G42" s="18">
+      <c r="G42" s="19">
         <v>0</v>
       </c>
-      <c r="H42" s="8">
+      <c r="H42" s="9">
         <v>1</v>
       </c>
       <c r="I42" s="4" t="s">
-        <v>309</v>
-      </c>
-      <c r="J42" s="10" t="s">
-        <v>310</v>
+        <v>319</v>
+      </c>
+      <c r="J42" s="11" t="s">
+        <v>320</v>
       </c>
       <c r="K42" s="4" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="L42" s="4">
         <v>2021</v>
       </c>
       <c r="M42" s="4" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="N42" s="4">
         <v>1</v>
@@ -17199,7 +17306,7 @@
         <v>14</v>
       </c>
       <c r="Q42" s="4" t="s">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="R42" s="4" t="s">
         <v>67</v>
@@ -17217,19 +17324,19 @@
         <v>6</v>
       </c>
       <c r="W42" s="4" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="X42" s="4" t="s">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="Y42" s="4" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="Z42" s="4" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="AA42" s="4" t="s">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="AB42" s="4" t="s">
         <v>61</v>
@@ -17255,13 +17362,13 @@
         <v>52</v>
       </c>
       <c r="AJ42" s="4" t="s">
-        <v>314</v>
-      </c>
-      <c r="AK42" s="11" t="s">
-        <v>315</v>
-      </c>
-      <c r="AL42" s="12" t="s">
-        <v>316</v>
+        <v>324</v>
+      </c>
+      <c r="AK42" s="12" t="s">
+        <v>325</v>
+      </c>
+      <c r="AL42" s="13" t="s">
+        <v>326</v>
       </c>
       <c r="AM42" s="4"/>
       <c r="AN42" s="4"/>
@@ -17528,37 +17635,37 @@
         <v>42</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>317</v>
+        <v>327</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>308</v>
-      </c>
-      <c r="E43" s="7" t="s">
+        <v>318</v>
+      </c>
+      <c r="E43" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="F43" s="8">
+      <c r="F43" s="9">
         <v>1</v>
       </c>
-      <c r="G43" s="18">
+      <c r="G43" s="19">
         <v>0</v>
       </c>
-      <c r="H43" s="8">
+      <c r="H43" s="9">
         <v>1</v>
       </c>
       <c r="I43" s="4" t="s">
-        <v>309</v>
-      </c>
-      <c r="J43" s="10" t="s">
-        <v>310</v>
+        <v>319</v>
+      </c>
+      <c r="J43" s="11" t="s">
+        <v>320</v>
       </c>
       <c r="K43" s="4" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="L43" s="4">
         <v>2021</v>
       </c>
       <c r="M43" s="4" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="N43" s="4">
         <v>1</v>
@@ -17570,7 +17677,7 @@
         <v>14</v>
       </c>
       <c r="Q43" s="4" t="s">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="R43" s="4" t="s">
         <v>67</v>
@@ -17588,19 +17695,19 @@
         <v>6</v>
       </c>
       <c r="W43" s="4" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="X43" s="4" t="s">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="Y43" s="4" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="Z43" s="4" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="AA43" s="4" t="s">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="AB43" s="4" t="s">
         <v>61</v>
@@ -17626,13 +17733,13 @@
         <v>52</v>
       </c>
       <c r="AJ43" s="4" t="s">
-        <v>314</v>
-      </c>
-      <c r="AK43" s="11" t="s">
-        <v>315</v>
-      </c>
-      <c r="AL43" s="12" t="s">
-        <v>316</v>
+        <v>324</v>
+      </c>
+      <c r="AK43" s="12" t="s">
+        <v>325</v>
+      </c>
+      <c r="AL43" s="13" t="s">
+        <v>326</v>
       </c>
       <c r="AM43" s="4"/>
       <c r="AN43" s="4"/>
@@ -17899,37 +18006,37 @@
         <v>43</v>
       </c>
       <c r="C44" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="D44" s="4" t="s">
         <v>318</v>
       </c>
-      <c r="D44" s="4" t="s">
-        <v>308</v>
-      </c>
-      <c r="E44" s="7" t="s">
+      <c r="E44" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="F44" s="8">
+      <c r="F44" s="9">
         <v>1</v>
       </c>
-      <c r="G44" s="18">
+      <c r="G44" s="19">
         <v>0</v>
       </c>
-      <c r="H44" s="8">
+      <c r="H44" s="9">
         <v>1</v>
       </c>
       <c r="I44" s="4" t="s">
-        <v>309</v>
-      </c>
-      <c r="J44" s="10" t="s">
-        <v>310</v>
+        <v>319</v>
+      </c>
+      <c r="J44" s="11" t="s">
+        <v>320</v>
       </c>
       <c r="K44" s="4" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="L44" s="4">
         <v>2021</v>
       </c>
       <c r="M44" s="4" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="N44" s="4">
         <v>1</v>
@@ -17941,7 +18048,7 @@
         <v>14</v>
       </c>
       <c r="Q44" s="4" t="s">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="R44" s="4" t="s">
         <v>67</v>
@@ -17959,19 +18066,19 @@
         <v>6</v>
       </c>
       <c r="W44" s="4" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="X44" s="4" t="s">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="Y44" s="4" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="Z44" s="4" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="AA44" s="4" t="s">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="AB44" s="4" t="s">
         <v>61</v>
@@ -17997,13 +18104,13 @@
         <v>52</v>
       </c>
       <c r="AJ44" s="4" t="s">
-        <v>314</v>
-      </c>
-      <c r="AK44" s="11" t="s">
-        <v>315</v>
-      </c>
-      <c r="AL44" s="12" t="s">
-        <v>316</v>
+        <v>324</v>
+      </c>
+      <c r="AK44" s="12" t="s">
+        <v>325</v>
+      </c>
+      <c r="AL44" s="13" t="s">
+        <v>326</v>
       </c>
       <c r="AM44" s="4"/>
       <c r="AN44" s="4"/>
@@ -18265,40 +18372,40 @@
       <c r="KJ44" s="4"/>
     </row>
     <row r="45" ht="15.5" spans="1:296">
-      <c r="A45" s="19" t="s">
-        <v>319</v>
+      <c r="A45" s="20" t="s">
+        <v>329</v>
       </c>
       <c r="B45" s="4">
         <v>44</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>321</v>
-      </c>
-      <c r="E45" s="7" t="s">
+        <v>331</v>
+      </c>
+      <c r="E45" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="F45" s="8">
+      <c r="F45" s="9">
         <v>1</v>
       </c>
-      <c r="G45" s="18">
+      <c r="G45" s="19">
         <v>0</v>
       </c>
-      <c r="H45" s="18">
+      <c r="H45" s="19">
         <v>0</v>
       </c>
       <c r="I45" s="4"/>
-      <c r="J45" s="10"/>
+      <c r="J45" s="11"/>
       <c r="K45" s="4" t="s">
-        <v>322</v>
+        <v>332</v>
       </c>
       <c r="L45" s="4">
         <v>2023</v>
       </c>
       <c r="M45" s="4" t="s">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="N45" s="4">
         <v>1</v>
@@ -18310,7 +18417,7 @@
         <v>14</v>
       </c>
       <c r="Q45" s="4" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="R45" s="4"/>
       <c r="S45" s="4">
@@ -18328,12 +18435,12 @@
       <c r="W45" s="4"/>
       <c r="X45" s="4"/>
       <c r="Y45" s="4" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="Z45" s="4"/>
       <c r="AA45" s="4"/>
       <c r="AB45" s="4" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="AC45" s="4">
         <v>40</v>
@@ -18352,7 +18459,7 @@
         <v>39</v>
       </c>
       <c r="AH45" s="4" t="s">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="AI45" s="4" t="s">
         <v>52</v>
@@ -18625,37 +18732,37 @@
         <v>45</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>325</v>
-      </c>
-      <c r="E46" s="7" t="s">
+        <v>335</v>
+      </c>
+      <c r="E46" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="F46" s="8">
+      <c r="F46" s="9">
         <v>1</v>
       </c>
-      <c r="G46" s="18">
+      <c r="G46" s="19">
         <v>0</v>
       </c>
-      <c r="H46" s="18">
+      <c r="H46" s="19">
         <v>0</v>
       </c>
       <c r="I46" s="4" t="s">
-        <v>326</v>
-      </c>
-      <c r="J46" s="10" t="s">
-        <v>327</v>
+        <v>336</v>
+      </c>
+      <c r="J46" s="11" t="s">
+        <v>337</v>
       </c>
       <c r="K46" s="4" t="s">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="L46" s="4">
         <v>2022</v>
       </c>
       <c r="M46" s="4" t="s">
-        <v>329</v>
+        <v>339</v>
       </c>
       <c r="N46" s="4">
         <v>1</v>
@@ -18683,20 +18790,20 @@
         <v>2</v>
       </c>
       <c r="W46" s="4" t="s">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="X46" s="4"/>
       <c r="Y46" s="4" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="Z46" s="4" t="s">
-        <v>332</v>
+        <v>342</v>
       </c>
       <c r="AA46" s="4" t="s">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="AB46" s="4" t="s">
-        <v>334</v>
+        <v>344</v>
       </c>
       <c r="AC46" s="4">
         <v>30</v>
@@ -18715,19 +18822,19 @@
         <v>27</v>
       </c>
       <c r="AH46" s="4" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="AI46" s="4" t="s">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="AJ46" s="4" t="s">
-        <v>337</v>
-      </c>
-      <c r="AK46" s="10" t="s">
-        <v>338</v>
+        <v>347</v>
+      </c>
+      <c r="AK46" s="11" t="s">
+        <v>348</v>
       </c>
       <c r="AL46" s="4" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="AM46" s="4"/>
       <c r="AN46" s="4"/>
@@ -18994,33 +19101,33 @@
         <v>46</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>339</v>
+        <v>349</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>325</v>
-      </c>
-      <c r="E47" s="7" t="s">
+        <v>335</v>
+      </c>
+      <c r="E47" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="F47" s="8">
+      <c r="F47" s="9">
         <v>1</v>
       </c>
-      <c r="G47" s="18">
+      <c r="G47" s="19">
         <v>0</v>
       </c>
-      <c r="H47" s="18">
+      <c r="H47" s="19">
         <v>0</v>
       </c>
       <c r="I47" s="4"/>
-      <c r="J47" s="10"/>
+      <c r="J47" s="11"/>
       <c r="K47" s="4" t="s">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="L47" s="4">
         <v>2022</v>
       </c>
       <c r="M47" s="4" t="s">
-        <v>329</v>
+        <v>339</v>
       </c>
       <c r="N47" s="4">
         <v>2</v>
@@ -19048,20 +19155,20 @@
         <v>2</v>
       </c>
       <c r="W47" s="4" t="s">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="X47" s="4"/>
       <c r="Y47" s="4" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="Z47" s="4" t="s">
-        <v>332</v>
+        <v>342</v>
       </c>
       <c r="AA47" s="4" t="s">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="AB47" s="4" t="s">
-        <v>334</v>
+        <v>344</v>
       </c>
       <c r="AC47" s="4">
         <v>104</v>
@@ -19080,19 +19187,19 @@
         <v>102</v>
       </c>
       <c r="AH47" s="4" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="AI47" s="4" t="s">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="AJ47" s="4" t="s">
-        <v>337</v>
-      </c>
-      <c r="AK47" s="10" t="s">
-        <v>338</v>
+        <v>347</v>
+      </c>
+      <c r="AK47" s="11" t="s">
+        <v>348</v>
       </c>
       <c r="AL47" s="4" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="AM47" s="4"/>
       <c r="AN47" s="4"/>
@@ -19355,43 +19462,43 @@
     </row>
     <row r="48" ht="15.5" spans="1:296">
       <c r="A48" s="4" t="s">
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="B48" s="4">
         <v>47</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>342</v>
-      </c>
-      <c r="E48" s="7" t="s">
+        <v>352</v>
+      </c>
+      <c r="E48" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="F48" s="8">
+      <c r="F48" s="9">
         <v>1</v>
       </c>
-      <c r="G48" s="8">
+      <c r="G48" s="9">
         <v>1</v>
       </c>
-      <c r="H48" s="18">
+      <c r="H48" s="19">
         <v>0</v>
       </c>
-      <c r="I48" s="20" t="s">
-        <v>343</v>
-      </c>
-      <c r="J48" s="10" t="s">
-        <v>344</v>
+      <c r="I48" s="21" t="s">
+        <v>353</v>
+      </c>
+      <c r="J48" s="11" t="s">
+        <v>354</v>
       </c>
       <c r="K48" s="4" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="L48" s="4">
         <v>2022</v>
       </c>
       <c r="M48" s="4" t="s">
-        <v>346</v>
+        <v>356</v>
       </c>
       <c r="N48" s="4">
         <v>1</v>
@@ -19403,7 +19510,7 @@
         <v>14</v>
       </c>
       <c r="Q48" s="4" t="s">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="R48" s="4" t="s">
         <v>67</v>
@@ -19423,13 +19530,13 @@
       <c r="W48" s="4"/>
       <c r="X48" s="4"/>
       <c r="Y48" s="4" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="Z48" s="4" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="AA48" s="4" t="s">
-        <v>347</v>
+        <v>357</v>
       </c>
       <c r="AB48" s="4" t="s">
         <v>61</v>
@@ -19438,7 +19545,7 @@
         <v>328</v>
       </c>
       <c r="AD48" s="1" t="s">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="AE48" s="1"/>
       <c r="AF48" s="4">
@@ -19453,13 +19560,13 @@
         <v>52</v>
       </c>
       <c r="AJ48" s="4" t="s">
-        <v>348</v>
-      </c>
-      <c r="AK48" s="11" t="s">
-        <v>349</v>
+        <v>358</v>
+      </c>
+      <c r="AK48" s="12" t="s">
+        <v>359</v>
       </c>
       <c r="AL48" s="4" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="AM48" s="4"/>
       <c r="AN48" s="4"/>
@@ -19726,37 +19833,37 @@
         <v>48</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>351</v>
-      </c>
-      <c r="E49" s="7" t="s">
+        <v>361</v>
+      </c>
+      <c r="E49" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="F49" s="8">
+      <c r="F49" s="9">
         <v>1</v>
       </c>
-      <c r="G49" s="18">
+      <c r="G49" s="19">
         <v>0</v>
       </c>
-      <c r="H49" s="18">
+      <c r="H49" s="19">
         <v>0</v>
       </c>
       <c r="I49" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="J49" s="10" t="s">
-        <v>352</v>
+        <v>172</v>
+      </c>
+      <c r="J49" s="11" t="s">
+        <v>362</v>
       </c>
       <c r="K49" s="4" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="L49" s="4">
         <v>2020</v>
       </c>
       <c r="M49" s="4" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="N49" s="4">
         <v>1</v>
@@ -19768,10 +19875,10 @@
         <v>14</v>
       </c>
       <c r="Q49" s="4" t="s">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="R49" s="4" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="S49" s="4">
         <v>24</v>
@@ -19788,7 +19895,7 @@
       <c r="W49" s="4"/>
       <c r="X49" s="4"/>
       <c r="Y49" s="4" t="s">
-        <v>353</v>
+        <v>363</v>
       </c>
       <c r="Z49" s="4"/>
       <c r="AA49" s="4"/>
@@ -19812,19 +19919,19 @@
         <v>18</v>
       </c>
       <c r="AH49" s="4" t="s">
-        <v>354</v>
+        <v>364</v>
       </c>
       <c r="AI49" s="4" t="s">
         <v>52</v>
       </c>
       <c r="AJ49" s="4" t="s">
-        <v>355</v>
-      </c>
-      <c r="AK49" s="11" t="s">
-        <v>356</v>
+        <v>365</v>
+      </c>
+      <c r="AK49" s="12" t="s">
+        <v>366</v>
       </c>
       <c r="AL49" s="4" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="AM49" s="4"/>
       <c r="AN49" s="4"/>
@@ -20091,33 +20198,33 @@
         <v>49</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>357</v>
+        <v>367</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>351</v>
-      </c>
-      <c r="E50" s="7" t="s">
+        <v>361</v>
+      </c>
+      <c r="E50" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="F50" s="8">
+      <c r="F50" s="9">
         <v>1</v>
       </c>
-      <c r="G50" s="18">
+      <c r="G50" s="19">
         <v>0</v>
       </c>
-      <c r="H50" s="18">
+      <c r="H50" s="19">
         <v>0</v>
       </c>
       <c r="I50" s="4"/>
-      <c r="J50" s="10"/>
+      <c r="J50" s="11"/>
       <c r="K50" s="4" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="L50" s="4">
         <v>2020</v>
       </c>
       <c r="M50" s="4" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="N50" s="4">
         <v>1</v>
@@ -20129,10 +20236,10 @@
         <v>14</v>
       </c>
       <c r="Q50" s="4" t="s">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="R50" s="4" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="S50" s="4">
         <v>24</v>
@@ -20149,7 +20256,7 @@
       <c r="W50" s="4"/>
       <c r="X50" s="4"/>
       <c r="Y50" s="4" t="s">
-        <v>353</v>
+        <v>363</v>
       </c>
       <c r="Z50" s="4"/>
       <c r="AA50" s="4"/>
@@ -20173,19 +20280,19 @@
         <v>18</v>
       </c>
       <c r="AH50" s="4" t="s">
-        <v>354</v>
+        <v>364</v>
       </c>
       <c r="AI50" s="4" t="s">
         <v>52</v>
       </c>
       <c r="AJ50" s="4" t="s">
-        <v>355</v>
-      </c>
-      <c r="AK50" s="10" t="s">
-        <v>356</v>
+        <v>365</v>
+      </c>
+      <c r="AK50" s="11" t="s">
+        <v>366</v>
       </c>
       <c r="AL50" s="4" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="AM50" s="4"/>
       <c r="AN50" s="4"/>
@@ -20452,33 +20559,33 @@
         <v>50</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>351</v>
-      </c>
-      <c r="E51" s="7" t="s">
+        <v>361</v>
+      </c>
+      <c r="E51" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="F51" s="8">
+      <c r="F51" s="9">
         <v>1</v>
       </c>
-      <c r="G51" s="18">
+      <c r="G51" s="19">
         <v>0</v>
       </c>
-      <c r="H51" s="18">
+      <c r="H51" s="19">
         <v>0</v>
       </c>
       <c r="I51" s="4"/>
-      <c r="J51" s="10"/>
+      <c r="J51" s="11"/>
       <c r="K51" s="4" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="L51" s="4">
         <v>2020</v>
       </c>
       <c r="M51" s="4" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="N51" s="4">
         <v>1</v>
@@ -20490,10 +20597,10 @@
         <v>14</v>
       </c>
       <c r="Q51" s="4" t="s">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="R51" s="4" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="S51" s="4">
         <v>24</v>
@@ -20510,7 +20617,7 @@
       <c r="W51" s="4"/>
       <c r="X51" s="4"/>
       <c r="Y51" s="4" t="s">
-        <v>353</v>
+        <v>363</v>
       </c>
       <c r="Z51" s="4"/>
       <c r="AA51" s="4"/>
@@ -20534,19 +20641,19 @@
         <v>18</v>
       </c>
       <c r="AH51" s="4" t="s">
-        <v>354</v>
+        <v>364</v>
       </c>
       <c r="AI51" s="4" t="s">
         <v>52</v>
       </c>
       <c r="AJ51" s="4" t="s">
-        <v>355</v>
-      </c>
-      <c r="AK51" s="10" t="s">
-        <v>356</v>
+        <v>365</v>
+      </c>
+      <c r="AK51" s="11" t="s">
+        <v>366</v>
       </c>
       <c r="AL51" s="4" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="AM51" s="4"/>
       <c r="AN51" s="4"/>
@@ -20813,37 +20920,37 @@
         <v>51</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>359</v>
+        <v>369</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>360</v>
-      </c>
-      <c r="E52" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="E52" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="F52" s="8">
+      <c r="F52" s="9">
         <v>1</v>
       </c>
-      <c r="G52" s="18">
+      <c r="G52" s="19">
         <v>0</v>
       </c>
-      <c r="H52" s="18">
+      <c r="H52" s="19">
         <v>0</v>
       </c>
-      <c r="I52" s="21" t="s">
-        <v>309</v>
-      </c>
-      <c r="J52" s="10" t="s">
-        <v>310</v>
+      <c r="I52" s="22" t="s">
+        <v>319</v>
+      </c>
+      <c r="J52" s="11" t="s">
+        <v>320</v>
       </c>
       <c r="K52" s="4" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="L52" s="4">
         <v>2023</v>
       </c>
       <c r="M52" s="4" t="s">
-        <v>362</v>
+        <v>372</v>
       </c>
       <c r="N52" s="4">
         <v>1</v>
@@ -20873,7 +20980,7 @@
       <c r="W52" s="4"/>
       <c r="X52" s="4"/>
       <c r="Y52" s="4" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="Z52" s="4"/>
       <c r="AA52" s="4"/>
@@ -20884,7 +20991,7 @@
         <v>380</v>
       </c>
       <c r="AD52" s="1" t="s">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="AE52" s="1"/>
       <c r="AF52" s="4">
@@ -20899,13 +21006,13 @@
         <v>52</v>
       </c>
       <c r="AJ52" s="4" t="s">
-        <v>363</v>
-      </c>
-      <c r="AK52" s="11" t="s">
-        <v>364</v>
+        <v>373</v>
+      </c>
+      <c r="AK52" s="12" t="s">
+        <v>374</v>
       </c>
       <c r="AL52" s="4" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="AM52" s="4"/>
       <c r="AN52" s="4"/>
@@ -21172,37 +21279,37 @@
         <v>52</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>366</v>
-      </c>
-      <c r="E53" s="7" t="s">
+        <v>376</v>
+      </c>
+      <c r="E53" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="F53" s="8">
+      <c r="F53" s="9">
         <v>1</v>
       </c>
-      <c r="G53" s="22" t="s">
-        <v>107</v>
-      </c>
-      <c r="H53" s="18">
+      <c r="G53" s="23" t="s">
+        <v>117</v>
+      </c>
+      <c r="H53" s="19">
         <v>0</v>
       </c>
       <c r="I53" s="4" t="s">
-        <v>367</v>
-      </c>
-      <c r="J53" s="10" t="s">
-        <v>368</v>
+        <v>377</v>
+      </c>
+      <c r="J53" s="11" t="s">
+        <v>378</v>
       </c>
       <c r="K53" s="4" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="L53" s="4">
         <v>2021</v>
       </c>
       <c r="M53" s="4" t="s">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="N53" s="4">
         <v>1</v>
@@ -21214,7 +21321,7 @@
         <v>14</v>
       </c>
       <c r="Q53" s="4" t="s">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="R53" s="4" t="s">
         <v>67</v>
@@ -21254,16 +21361,16 @@
       </c>
       <c r="AH53" s="4"/>
       <c r="AI53" s="4" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="AJ53" s="4" t="s">
-        <v>371</v>
-      </c>
-      <c r="AK53" s="12" t="s">
-        <v>372</v>
+        <v>381</v>
+      </c>
+      <c r="AK53" s="13" t="s">
+        <v>382</v>
       </c>
       <c r="AL53" s="4" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="AM53" s="4"/>
       <c r="AN53" s="4"/>
@@ -21530,37 +21637,37 @@
         <v>53</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>373</v>
+        <v>383</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>374</v>
-      </c>
-      <c r="E54" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="E54" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="F54" s="8">
+      <c r="F54" s="9">
         <v>1</v>
       </c>
-      <c r="G54" s="18">
+      <c r="G54" s="19">
         <v>0</v>
       </c>
-      <c r="H54" s="8">
+      <c r="H54" s="9">
         <v>1</v>
       </c>
-      <c r="I54" s="21" t="s">
-        <v>375</v>
-      </c>
-      <c r="J54" s="11" t="s">
-        <v>376</v>
+      <c r="I54" s="22" t="s">
+        <v>385</v>
+      </c>
+      <c r="J54" s="12" t="s">
+        <v>386</v>
       </c>
       <c r="K54" s="4" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="L54" s="4">
         <v>2023</v>
       </c>
       <c r="M54" s="4" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="N54" s="4">
         <v>1</v>
@@ -21572,7 +21679,7 @@
         <v>14</v>
       </c>
       <c r="Q54" s="4" t="s">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="R54" s="4" t="s">
         <v>67</v>
@@ -21611,19 +21718,19 @@
         <v>20</v>
       </c>
       <c r="AH54" s="4" t="s">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="AI54" s="4" t="s">
         <v>52</v>
       </c>
       <c r="AJ54" s="4" t="s">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="AK54" s="4" t="s">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="AL54" s="4" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="AM54" s="4"/>
       <c r="AN54" s="4"/>
@@ -21890,37 +21997,37 @@
         <v>54</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>383</v>
-      </c>
-      <c r="E55" s="7" t="s">
+        <v>393</v>
+      </c>
+      <c r="E55" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="F55" s="8">
+      <c r="F55" s="9">
         <v>1</v>
       </c>
-      <c r="G55" s="18">
+      <c r="G55" s="19">
         <v>0</v>
       </c>
-      <c r="H55" s="18">
+      <c r="H55" s="19">
         <v>0</v>
       </c>
-      <c r="I55" s="21" t="s">
-        <v>384</v>
-      </c>
-      <c r="J55" s="10" t="s">
-        <v>385</v>
+      <c r="I55" s="22" t="s">
+        <v>394</v>
+      </c>
+      <c r="J55" s="11" t="s">
+        <v>395</v>
       </c>
       <c r="K55" s="4" t="s">
-        <v>386</v>
+        <v>396</v>
       </c>
       <c r="L55" s="4">
         <v>2024</v>
       </c>
       <c r="M55" s="4" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="N55" s="4">
         <v>1</v>
@@ -21932,7 +22039,7 @@
         <v>14</v>
       </c>
       <c r="Q55" s="4" t="s">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="R55" s="4" t="s">
         <v>67</v>
@@ -21952,12 +22059,12 @@
       <c r="W55" s="4"/>
       <c r="X55" s="4"/>
       <c r="Y55" s="4" t="s">
-        <v>387</v>
+        <v>397</v>
       </c>
       <c r="Z55" s="4"/>
       <c r="AA55" s="4"/>
       <c r="AB55" s="4" t="s">
-        <v>388</v>
+        <v>398</v>
       </c>
       <c r="AC55" s="4">
         <v>32</v>
@@ -21975,19 +22082,19 @@
         <v>32</v>
       </c>
       <c r="AH55" s="4" t="s">
-        <v>389</v>
+        <v>399</v>
       </c>
       <c r="AI55" s="4" t="s">
         <v>52</v>
       </c>
       <c r="AJ55" s="4" t="s">
-        <v>390</v>
-      </c>
-      <c r="AK55" s="10" t="s">
-        <v>391</v>
+        <v>400</v>
+      </c>
+      <c r="AK55" s="11" t="s">
+        <v>401</v>
       </c>
       <c r="AL55" s="4" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="AM55" s="4"/>
       <c r="AN55" s="4"/>
@@ -22254,37 +22361,37 @@
         <v>55</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>392</v>
+        <v>402</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>393</v>
-      </c>
-      <c r="E56" s="7" t="s">
+        <v>403</v>
+      </c>
+      <c r="E56" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="F56" s="8">
+      <c r="F56" s="9">
         <v>1</v>
       </c>
-      <c r="G56" s="22" t="s">
-        <v>107</v>
-      </c>
-      <c r="H56" s="8">
+      <c r="G56" s="23" t="s">
+        <v>117</v>
+      </c>
+      <c r="H56" s="9">
         <v>1</v>
       </c>
       <c r="I56" s="4" t="s">
-        <v>394</v>
-      </c>
-      <c r="J56" s="10" t="s">
-        <v>395</v>
+        <v>404</v>
+      </c>
+      <c r="J56" s="11" t="s">
+        <v>405</v>
       </c>
       <c r="K56" s="4" t="s">
-        <v>396</v>
+        <v>406</v>
       </c>
       <c r="L56" s="4">
         <v>2024</v>
       </c>
       <c r="M56" s="4" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="N56" s="4">
         <v>1</v>
@@ -22296,7 +22403,7 @@
         <v>14</v>
       </c>
       <c r="Q56" s="4" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="R56" s="4" t="s">
         <v>67</v>
@@ -22331,19 +22438,19 @@
       <c r="AF56" s="4"/>
       <c r="AG56" s="4"/>
       <c r="AH56" s="4" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="AI56" s="4" t="s">
         <v>52</v>
       </c>
       <c r="AJ56" s="4" t="s">
-        <v>400</v>
-      </c>
-      <c r="AK56" s="11" t="s">
-        <v>401</v>
-      </c>
-      <c r="AL56" s="12" t="s">
-        <v>402</v>
+        <v>410</v>
+      </c>
+      <c r="AK56" s="12" t="s">
+        <v>411</v>
+      </c>
+      <c r="AL56" s="13" t="s">
+        <v>412</v>
       </c>
       <c r="AM56" s="4"/>
       <c r="AN56" s="4"/>
@@ -22610,37 +22717,37 @@
         <v>56</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>404</v>
-      </c>
-      <c r="E57" s="7" t="s">
+        <v>414</v>
+      </c>
+      <c r="E57" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="F57" s="8">
+      <c r="F57" s="9">
         <v>1</v>
       </c>
-      <c r="G57" s="18">
+      <c r="G57" s="19">
         <v>0</v>
       </c>
-      <c r="H57" s="18">
+      <c r="H57" s="19">
         <v>0</v>
       </c>
-      <c r="I57" s="21" t="s">
-        <v>375</v>
-      </c>
-      <c r="J57" s="11" t="s">
-        <v>376</v>
+      <c r="I57" s="22" t="s">
+        <v>385</v>
+      </c>
+      <c r="J57" s="12" t="s">
+        <v>386</v>
       </c>
       <c r="K57" s="4" t="s">
-        <v>405</v>
+        <v>415</v>
       </c>
       <c r="L57" s="4">
         <v>2015</v>
       </c>
       <c r="M57" s="4" t="s">
-        <v>329</v>
+        <v>339</v>
       </c>
       <c r="N57" s="4">
         <v>1</v>
@@ -22668,11 +22775,11 @@
         <v>52</v>
       </c>
       <c r="AJ57" s="4" t="s">
-        <v>406</v>
-      </c>
-      <c r="AK57" s="10"/>
+        <v>416</v>
+      </c>
+      <c r="AK57" s="11"/>
       <c r="AL57" s="4" t="s">
-        <v>407</v>
+        <v>417</v>
       </c>
       <c r="AM57" s="4"/>
       <c r="AN57" s="4"/>
@@ -22939,37 +23046,37 @@
         <v>57</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>408</v>
+        <v>418</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>409</v>
-      </c>
-      <c r="E58" s="7" t="s">
+        <v>419</v>
+      </c>
+      <c r="E58" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="F58" s="8">
+      <c r="F58" s="9">
         <v>1</v>
       </c>
-      <c r="G58" s="18">
+      <c r="G58" s="19">
         <v>0</v>
       </c>
-      <c r="H58" s="18">
+      <c r="H58" s="19">
         <v>0</v>
       </c>
-      <c r="I58" s="21" t="s">
-        <v>410</v>
-      </c>
-      <c r="J58" s="10" t="s">
-        <v>411</v>
-      </c>
-      <c r="K58" s="21" t="s">
-        <v>412</v>
+      <c r="I58" s="22" t="s">
+        <v>420</v>
+      </c>
+      <c r="J58" s="11" t="s">
+        <v>421</v>
+      </c>
+      <c r="K58" s="22" t="s">
+        <v>422</v>
       </c>
       <c r="L58" s="4">
         <v>2024</v>
       </c>
       <c r="M58" s="4" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="N58" s="4">
         <v>1</v>
@@ -22982,7 +23089,7 @@
       </c>
       <c r="Q58" s="4"/>
       <c r="R58" s="4" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="S58" s="4"/>
       <c r="T58" s="4"/>
@@ -22991,12 +23098,12 @@
       <c r="W58" s="4"/>
       <c r="X58" s="4"/>
       <c r="Y58" s="4" t="s">
-        <v>413</v>
+        <v>423</v>
       </c>
       <c r="Z58" s="4"/>
       <c r="AA58" s="4"/>
       <c r="AB58" s="4" t="s">
-        <v>414</v>
+        <v>424</v>
       </c>
       <c r="AC58" s="4">
         <v>40</v>
@@ -23014,19 +23121,19 @@
         <v>40</v>
       </c>
       <c r="AH58" s="4" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="AI58" s="4" t="s">
-        <v>416</v>
+        <v>426</v>
       </c>
       <c r="AJ58" s="4" t="s">
-        <v>417</v>
-      </c>
-      <c r="AK58" s="11" t="s">
-        <v>418</v>
+        <v>427</v>
+      </c>
+      <c r="AK58" s="12" t="s">
+        <v>428</v>
       </c>
       <c r="AL58" s="4" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="AM58" s="4"/>
       <c r="AN58" s="4"/>
@@ -23293,37 +23400,37 @@
         <v>58</v>
       </c>
       <c r="C59" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="D59" s="4" t="s">
         <v>419</v>
       </c>
-      <c r="D59" s="4" t="s">
-        <v>409</v>
-      </c>
-      <c r="E59" s="7" t="s">
+      <c r="E59" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="F59" s="8">
+      <c r="F59" s="9">
         <v>1</v>
       </c>
-      <c r="G59" s="18">
+      <c r="G59" s="19">
         <v>0</v>
       </c>
-      <c r="H59" s="18">
+      <c r="H59" s="19">
         <v>0</v>
       </c>
-      <c r="I59" s="21" t="s">
-        <v>410</v>
-      </c>
-      <c r="J59" s="10" t="s">
-        <v>411</v>
-      </c>
-      <c r="K59" s="21" t="s">
-        <v>412</v>
+      <c r="I59" s="22" t="s">
+        <v>420</v>
+      </c>
+      <c r="J59" s="11" t="s">
+        <v>421</v>
+      </c>
+      <c r="K59" s="22" t="s">
+        <v>422</v>
       </c>
       <c r="L59" s="4">
         <v>2024</v>
       </c>
       <c r="M59" s="4" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="N59" s="4">
         <v>2</v>
@@ -23336,7 +23443,7 @@
       </c>
       <c r="Q59" s="4"/>
       <c r="R59" s="4" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="S59" s="4"/>
       <c r="T59" s="4"/>
@@ -23345,12 +23452,12 @@
       <c r="W59" s="4"/>
       <c r="X59" s="4"/>
       <c r="Y59" s="4" t="s">
-        <v>413</v>
+        <v>423</v>
       </c>
       <c r="Z59" s="4"/>
       <c r="AA59" s="4"/>
       <c r="AB59" s="4" t="s">
-        <v>414</v>
+        <v>424</v>
       </c>
       <c r="AC59" s="4">
         <v>40</v>
@@ -23368,19 +23475,19 @@
         <v>40</v>
       </c>
       <c r="AH59" s="4" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="AI59" s="4" t="s">
-        <v>416</v>
+        <v>426</v>
       </c>
       <c r="AJ59" s="4" t="s">
-        <v>417</v>
-      </c>
-      <c r="AK59" s="11" t="s">
-        <v>418</v>
+        <v>427</v>
+      </c>
+      <c r="AK59" s="12" t="s">
+        <v>428</v>
       </c>
       <c r="AL59" s="4" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="AM59" s="4"/>
       <c r="AN59" s="4"/>
@@ -23647,25 +23754,25 @@
         <v>59</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>420</v>
+        <v>430</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>421</v>
-      </c>
-      <c r="E60" s="7" t="s">
+        <v>431</v>
+      </c>
+      <c r="E60" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="F60" s="8">
+      <c r="F60" s="9">
         <v>1</v>
       </c>
-      <c r="G60" s="18">
+      <c r="G60" s="19">
         <v>0</v>
       </c>
-      <c r="H60" s="8">
+      <c r="H60" s="9">
         <v>1</v>
       </c>
       <c r="I60" s="4"/>
-      <c r="J60" s="10"/>
+      <c r="J60" s="11"/>
       <c r="K60" s="4"/>
       <c r="L60" s="4"/>
       <c r="M60" s="4"/>
@@ -23691,16 +23798,16 @@
       <c r="AG60" s="4"/>
       <c r="AH60" s="4"/>
       <c r="AI60" s="4" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="AJ60" s="4" t="s">
-        <v>422</v>
-      </c>
-      <c r="AK60" s="10" t="s">
-        <v>423</v>
+        <v>432</v>
+      </c>
+      <c r="AK60" s="11" t="s">
+        <v>433</v>
       </c>
       <c r="AL60" s="4" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="AM60" s="4"/>
       <c r="AN60" s="4"/>
@@ -23967,37 +24074,37 @@
         <v>60</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>425</v>
-      </c>
-      <c r="E61" s="7" t="s">
+        <v>435</v>
+      </c>
+      <c r="E61" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="F61" s="8">
+      <c r="F61" s="9">
         <v>1</v>
       </c>
-      <c r="G61" s="18">
+      <c r="G61" s="19">
         <v>0</v>
       </c>
-      <c r="H61" s="18">
+      <c r="H61" s="19">
         <v>0</v>
       </c>
       <c r="I61" s="4" t="s">
-        <v>426</v>
-      </c>
-      <c r="J61" s="10" t="s">
-        <v>427</v>
+        <v>436</v>
+      </c>
+      <c r="J61" s="11" t="s">
+        <v>437</v>
       </c>
       <c r="K61" s="4" t="s">
-        <v>428</v>
+        <v>438</v>
       </c>
       <c r="L61" s="4">
         <v>2024</v>
       </c>
       <c r="M61" s="4" t="s">
-        <v>429</v>
+        <v>439</v>
       </c>
       <c r="N61" s="4">
         <v>1</v>
@@ -24006,13 +24113,13 @@
         <v>1</v>
       </c>
       <c r="P61" s="4" t="s">
-        <v>430</v>
+        <v>440</v>
       </c>
       <c r="Q61" s="4" t="s">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="R61" s="4" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="S61" s="4"/>
       <c r="T61" s="4"/>
@@ -24031,16 +24138,16 @@
       <c r="AG61" s="4"/>
       <c r="AH61" s="4"/>
       <c r="AI61" s="4" t="s">
-        <v>416</v>
+        <v>426</v>
       </c>
       <c r="AJ61" s="4" t="s">
-        <v>431</v>
-      </c>
-      <c r="AK61" s="10" t="s">
-        <v>432</v>
+        <v>441</v>
+      </c>
+      <c r="AK61" s="11" t="s">
+        <v>442</v>
       </c>
       <c r="AL61" s="4" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="AM61" s="4"/>
       <c r="AN61" s="4"/>
@@ -24307,37 +24414,37 @@
         <v>61</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>433</v>
+        <v>443</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>425</v>
-      </c>
-      <c r="E62" s="7" t="s">
+        <v>435</v>
+      </c>
+      <c r="E62" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="F62" s="8">
+      <c r="F62" s="9">
         <v>1</v>
       </c>
-      <c r="G62" s="18">
+      <c r="G62" s="19">
         <v>0</v>
       </c>
-      <c r="H62" s="18">
+      <c r="H62" s="19">
         <v>0</v>
       </c>
       <c r="I62" s="4" t="s">
-        <v>426</v>
-      </c>
-      <c r="J62" s="10" t="s">
-        <v>427</v>
+        <v>436</v>
+      </c>
+      <c r="J62" s="11" t="s">
+        <v>437</v>
       </c>
       <c r="K62" s="4" t="s">
-        <v>428</v>
+        <v>438</v>
       </c>
       <c r="L62" s="4">
         <v>2024</v>
       </c>
       <c r="M62" s="4" t="s">
-        <v>429</v>
+        <v>439</v>
       </c>
       <c r="N62" s="4">
         <v>1</v>
@@ -24346,13 +24453,13 @@
         <v>1</v>
       </c>
       <c r="P62" s="4" t="s">
-        <v>430</v>
+        <v>440</v>
       </c>
       <c r="Q62" s="4" t="s">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="R62" s="4" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="S62" s="4"/>
       <c r="T62" s="4"/>
@@ -24371,16 +24478,16 @@
       <c r="AG62" s="4"/>
       <c r="AH62" s="4"/>
       <c r="AI62" s="4" t="s">
-        <v>416</v>
+        <v>426</v>
       </c>
       <c r="AJ62" s="4" t="s">
-        <v>431</v>
-      </c>
-      <c r="AK62" s="10" t="s">
-        <v>432</v>
+        <v>441</v>
+      </c>
+      <c r="AK62" s="11" t="s">
+        <v>442</v>
       </c>
       <c r="AL62" s="4" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="AM62" s="4"/>
       <c r="AN62" s="4"/>
@@ -24647,17 +24754,17 @@
         <v>62</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>434</v>
+        <v>444</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>435</v>
+        <v>445</v>
       </c>
       <c r="E63" s="4"/>
       <c r="F63" s="4"/>
       <c r="G63" s="4"/>
       <c r="H63" s="4"/>
       <c r="I63" s="4"/>
-      <c r="J63" s="10"/>
+      <c r="J63" s="11"/>
       <c r="K63" s="4"/>
       <c r="L63" s="4"/>
       <c r="M63" s="4"/>
@@ -24684,9 +24791,9 @@
       <c r="AH63" s="4"/>
       <c r="AI63" s="4"/>
       <c r="AJ63" s="4" t="s">
-        <v>436</v>
-      </c>
-      <c r="AK63" s="10"/>
+        <v>446</v>
+      </c>
+      <c r="AK63" s="11"/>
       <c r="AL63" s="4"/>
       <c r="AM63" s="4"/>
       <c r="AN63" s="4"/>
@@ -24953,17 +25060,17 @@
         <v>63</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>437</v>
+        <v>447</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>435</v>
+        <v>445</v>
       </c>
       <c r="E64" s="4"/>
       <c r="F64" s="4"/>
       <c r="G64" s="4"/>
       <c r="H64" s="4"/>
       <c r="I64" s="4"/>
-      <c r="J64" s="10"/>
+      <c r="J64" s="11"/>
       <c r="K64" s="4"/>
       <c r="L64" s="4"/>
       <c r="M64" s="4"/>
@@ -24990,9 +25097,9 @@
       <c r="AH64" s="4"/>
       <c r="AI64" s="4"/>
       <c r="AJ64" s="4" t="s">
-        <v>436</v>
-      </c>
-      <c r="AK64" s="10"/>
+        <v>446</v>
+      </c>
+      <c r="AK64" s="11"/>
       <c r="AL64" s="4"/>
       <c r="AM64" s="4"/>
       <c r="AN64" s="4"/>
@@ -25255,23 +25362,23 @@
     </row>
     <row r="65" ht="15.5" spans="1:296">
       <c r="A65" s="4" t="s">
-        <v>438</v>
+        <v>448</v>
       </c>
       <c r="B65" s="4">
         <v>64</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>439</v>
+        <v>449</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>440</v>
+        <v>450</v>
       </c>
       <c r="E65" s="4"/>
       <c r="F65" s="4"/>
       <c r="G65" s="4"/>
       <c r="H65" s="4"/>
       <c r="I65" s="4"/>
-      <c r="J65" s="10"/>
+      <c r="J65" s="11"/>
       <c r="K65" s="4"/>
       <c r="L65" s="4"/>
       <c r="M65" s="4"/>
@@ -25298,9 +25405,9 @@
       <c r="AH65" s="4"/>
       <c r="AI65" s="4"/>
       <c r="AJ65" s="4" t="s">
-        <v>441</v>
-      </c>
-      <c r="AK65" s="10"/>
+        <v>451</v>
+      </c>
+      <c r="AK65" s="11"/>
       <c r="AL65" s="4"/>
       <c r="AM65" s="4"/>
       <c r="AN65" s="4"/>
@@ -25567,17 +25674,17 @@
         <v>65</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>443</v>
+        <v>453</v>
       </c>
       <c r="E66" s="4"/>
       <c r="F66" s="4"/>
       <c r="G66" s="4"/>
       <c r="H66" s="4"/>
       <c r="I66" s="4"/>
-      <c r="J66" s="10"/>
+      <c r="J66" s="11"/>
       <c r="K66" s="4"/>
       <c r="L66" s="4"/>
       <c r="M66" s="4"/>
@@ -25604,9 +25711,9 @@
       <c r="AH66" s="4"/>
       <c r="AI66" s="4"/>
       <c r="AJ66" t="s">
-        <v>444</v>
-      </c>
-      <c r="AK66" s="10"/>
+        <v>454</v>
+      </c>
+      <c r="AK66" s="11"/>
       <c r="AL66" s="4"/>
       <c r="AM66" s="4"/>
       <c r="AN66" s="4"/>
@@ -25873,17 +25980,17 @@
         <v>66</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>445</v>
+        <v>455</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>446</v>
+        <v>456</v>
       </c>
       <c r="E67" s="4"/>
       <c r="F67" s="4"/>
       <c r="G67" s="4"/>
       <c r="H67" s="4"/>
       <c r="I67" s="4"/>
-      <c r="J67" s="10"/>
+      <c r="J67" s="11"/>
       <c r="K67" s="4"/>
       <c r="L67" s="4"/>
       <c r="M67" s="4"/>
@@ -25910,9 +26017,9 @@
       <c r="AH67" s="4"/>
       <c r="AI67" s="4"/>
       <c r="AJ67" s="4" t="s">
-        <v>447</v>
-      </c>
-      <c r="AK67" s="10"/>
+        <v>457</v>
+      </c>
+      <c r="AK67" s="11"/>
       <c r="AL67" s="4"/>
       <c r="AM67" s="4"/>
       <c r="AN67" s="4"/>
@@ -26179,17 +26286,17 @@
         <v>67</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>448</v>
+        <v>458</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>449</v>
+        <v>459</v>
       </c>
       <c r="E68" s="4"/>
       <c r="F68" s="4"/>
       <c r="G68" s="4"/>
       <c r="H68" s="4"/>
       <c r="I68" s="4"/>
-      <c r="J68" s="10"/>
+      <c r="J68" s="11"/>
       <c r="K68" s="4"/>
       <c r="L68" s="4"/>
       <c r="M68" s="4"/>
@@ -26216,9 +26323,9 @@
       <c r="AH68" s="4"/>
       <c r="AI68" s="4"/>
       <c r="AJ68" s="4" t="s">
-        <v>450</v>
-      </c>
-      <c r="AK68" s="10"/>
+        <v>460</v>
+      </c>
+      <c r="AK68" s="11"/>
       <c r="AL68" s="4"/>
       <c r="AM68" s="4"/>
       <c r="AN68" s="4"/>
@@ -26485,17 +26592,17 @@
         <v>68</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>451</v>
+        <v>461</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>449</v>
+        <v>459</v>
       </c>
       <c r="E69" s="4"/>
       <c r="F69" s="4"/>
       <c r="G69" s="4"/>
       <c r="H69" s="4"/>
       <c r="I69" s="4"/>
-      <c r="J69" s="10"/>
+      <c r="J69" s="11"/>
       <c r="K69" s="4"/>
       <c r="L69" s="4"/>
       <c r="M69" s="4"/>
@@ -26522,9 +26629,9 @@
       <c r="AH69" s="4"/>
       <c r="AI69" s="4"/>
       <c r="AJ69" s="4" t="s">
-        <v>450</v>
-      </c>
-      <c r="AK69" s="10"/>
+        <v>460</v>
+      </c>
+      <c r="AK69" s="11"/>
       <c r="AL69" s="4"/>
       <c r="AM69" s="4"/>
       <c r="AN69" s="4"/>
@@ -26791,17 +26898,17 @@
         <v>69</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>452</v>
+        <v>462</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>453</v>
+        <v>463</v>
       </c>
       <c r="E70" s="4"/>
       <c r="F70" s="4"/>
       <c r="G70" s="4"/>
       <c r="H70" s="4"/>
       <c r="I70" s="4"/>
-      <c r="J70" s="10"/>
+      <c r="J70" s="11"/>
       <c r="K70" s="4"/>
       <c r="L70" s="4"/>
       <c r="M70" s="4"/>
@@ -26828,9 +26935,9 @@
       <c r="AH70" s="4"/>
       <c r="AI70" s="4"/>
       <c r="AJ70" s="4" t="s">
-        <v>454</v>
-      </c>
-      <c r="AK70" s="10"/>
+        <v>464</v>
+      </c>
+      <c r="AK70" s="11"/>
       <c r="AL70" s="4"/>
       <c r="AM70" s="4"/>
       <c r="AN70" s="4"/>
@@ -27101,7 +27208,7 @@
       <c r="G71" s="4"/>
       <c r="H71" s="4"/>
       <c r="I71" s="4"/>
-      <c r="J71" s="10"/>
+      <c r="J71" s="11"/>
       <c r="K71" s="4"/>
       <c r="L71" s="4"/>
       <c r="M71" s="4"/>
@@ -27128,7 +27235,7 @@
       <c r="AH71" s="4"/>
       <c r="AI71" s="4"/>
       <c r="AJ71" s="4"/>
-      <c r="AK71" s="10"/>
+      <c r="AK71" s="11"/>
       <c r="AL71" s="4"/>
       <c r="AM71" s="4"/>
       <c r="AN71" s="4"/>
@@ -27399,7 +27506,7 @@
       <c r="G72" s="4"/>
       <c r="H72" s="4"/>
       <c r="I72" s="4"/>
-      <c r="J72" s="10"/>
+      <c r="J72" s="11"/>
       <c r="K72" s="4"/>
       <c r="L72" s="4"/>
       <c r="M72" s="4"/>
@@ -27426,7 +27533,7 @@
       <c r="AH72" s="4"/>
       <c r="AI72" s="4"/>
       <c r="AJ72" s="4"/>
-      <c r="AK72" s="10"/>
+      <c r="AK72" s="11"/>
       <c r="AL72" s="4"/>
       <c r="AM72" s="4"/>
       <c r="AN72" s="4"/>
@@ -27697,7 +27804,7 @@
       <c r="G73" s="4"/>
       <c r="H73" s="4"/>
       <c r="I73" s="4"/>
-      <c r="J73" s="10"/>
+      <c r="J73" s="11"/>
       <c r="K73" s="4"/>
       <c r="L73" s="4"/>
       <c r="M73" s="4"/>
@@ -27724,7 +27831,7 @@
       <c r="AH73" s="4"/>
       <c r="AI73" s="4"/>
       <c r="AJ73" s="4"/>
-      <c r="AK73" s="10"/>
+      <c r="AK73" s="11"/>
       <c r="AL73" s="4"/>
       <c r="AM73" s="4"/>
       <c r="AN73" s="4"/>
@@ -27992,7 +28099,7 @@
       <c r="D74" s="4"/>
       <c r="E74" s="4"/>
       <c r="I74" s="4"/>
-      <c r="J74" s="10"/>
+      <c r="J74" s="11"/>
       <c r="K74" s="4"/>
       <c r="L74" s="4"/>
       <c r="M74" s="4"/>
@@ -28001,7 +28108,7 @@
       <c r="P74" s="4"/>
       <c r="Q74" s="4"/>
       <c r="R74" s="4"/>
-      <c r="AK74" s="10"/>
+      <c r="AK74" s="11"/>
     </row>
     <row r="75" ht="15.5" spans="1:296">
       <c r="M75" s="4"/>
@@ -28088,8 +28195,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D68"/>
-  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="14" outlineLevelCol="3"/>
+  <dimension ref="A1:L67"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="3.625" customWidth="1"/>
     <col min="2" max="2" width="9.16666666666667" customWidth="1"/>
@@ -28097,7 +28204,7 @@
     <col min="4" max="4" width="25.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.5" spans="1:4">
+    <row r="1" ht="15.5" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -28111,7 +28218,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" ht="15.5" spans="1:4">
+    <row r="2" ht="15.5" spans="1:12">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -28125,7 +28232,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="3" ht="15.5" spans="1:4">
+    <row r="3" ht="15.5" spans="1:12">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -28139,7 +28246,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="4" ht="15.5" spans="1:4">
+    <row r="4" ht="15.5" spans="1:12">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -28153,7 +28260,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="5" ht="15.5" spans="1:4">
+    <row r="5" ht="15.5" spans="1:12">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -28167,7 +28274,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="6" ht="15.5" spans="1:4">
+    <row r="6" ht="15.5" spans="1:12">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -28180,145 +28287,146 @@
       <c r="D6" s="4" t="s">
         <v>73</v>
       </c>
+      <c r="L6" s="5"/>
     </row>
-    <row r="7" ht="15.5" spans="1:4">
+    <row r="7" ht="15.5" spans="1:12">
       <c r="A7" s="4">
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
     </row>
-    <row r="8" ht="15.5" spans="1:4">
+    <row r="8" ht="15.5" spans="1:12">
       <c r="A8" s="4">
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
     </row>
-    <row r="9" ht="15.5" spans="1:4">
+    <row r="9" ht="15.5" spans="1:12">
       <c r="A9" s="4">
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
     </row>
-    <row r="10" ht="15.5" spans="1:4">
+    <row r="10" ht="15.5" spans="1:12">
       <c r="A10" s="4">
         <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
     </row>
-    <row r="11" ht="15.5" spans="1:4">
+    <row r="11" ht="15.5" spans="1:12">
       <c r="A11" s="4">
         <v>10</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
     </row>
-    <row r="12" ht="15.5" spans="1:4">
+    <row r="12" ht="15.5" spans="1:12">
       <c r="A12" s="4">
         <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
     </row>
-    <row r="13" ht="15.5" spans="1:4">
+    <row r="13" ht="15.5" spans="1:12">
       <c r="A13" s="4">
         <v>12</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
     </row>
-    <row r="14" ht="15.5" spans="1:4">
+    <row r="14" ht="15.5" spans="1:12">
       <c r="A14" s="4">
         <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
     </row>
-    <row r="15" ht="15.5" spans="1:4">
+    <row r="15" ht="15.5" spans="1:12">
       <c r="A15" s="4">
         <v>14</v>
       </c>
       <c r="B15" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="C15" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="C15" s="4" t="s">
-        <v>161</v>
-      </c>
       <c r="D15" s="4" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
     </row>
-    <row r="16" ht="15.5" spans="1:4">
+    <row r="16" ht="15.5" spans="1:12">
       <c r="A16" s="4">
         <v>15</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
     </row>
     <row r="17" ht="15.5" spans="1:4">
@@ -28326,13 +28434,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
     </row>
     <row r="18" ht="15.5" spans="1:4">
@@ -28340,13 +28448,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
     </row>
     <row r="19" ht="15.5" spans="1:4">
@@ -28354,13 +28462,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="C19" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="C19" s="4" t="s">
-        <v>186</v>
-      </c>
       <c r="D19" s="4" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
     </row>
     <row r="20" ht="15.5" spans="1:4">
@@ -28368,13 +28476,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
     </row>
     <row r="21" ht="15.5" spans="1:4">
@@ -28382,13 +28490,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
     </row>
     <row r="22" ht="15.5" spans="1:4">
@@ -28396,13 +28504,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
     </row>
     <row r="23" ht="15.5" spans="1:4">
@@ -28410,13 +28518,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
     </row>
     <row r="24" ht="15.5" spans="1:4">
@@ -28424,13 +28532,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
     </row>
     <row r="25" ht="15.5" spans="1:4">
@@ -28438,13 +28546,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
     </row>
     <row r="26" ht="15.5" spans="1:4">
@@ -28452,13 +28560,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
     </row>
     <row r="27" ht="15.5" spans="1:4">
@@ -28466,13 +28574,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
     </row>
     <row r="28" ht="15.5" spans="1:4">
@@ -28480,13 +28588,13 @@
         <v>27</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
     </row>
     <row r="29" ht="15.5" spans="1:4">
@@ -28494,13 +28602,13 @@
         <v>28</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
     </row>
     <row r="30" ht="15.5" spans="1:4">
@@ -28508,13 +28616,13 @@
         <v>29</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>259</v>
+        <v>269</v>
       </c>
     </row>
     <row r="31" ht="15.5" spans="1:4">
@@ -28522,13 +28630,13 @@
         <v>30</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
     </row>
     <row r="32" ht="15.5" spans="1:4">
@@ -28536,13 +28644,13 @@
         <v>31</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>267</v>
+        <v>277</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>268</v>
+        <v>278</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
     </row>
     <row r="33" ht="15.5" spans="1:4">
@@ -28550,13 +28658,13 @@
         <v>32</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>268</v>
+        <v>278</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
     </row>
     <row r="34" ht="15.5" spans="1:4">
@@ -28564,13 +28672,13 @@
         <v>33</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
     </row>
     <row r="35" ht="15.5" spans="1:4">
@@ -28578,13 +28686,13 @@
         <v>34</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>281</v>
+        <v>291</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
     </row>
     <row r="36" ht="15.5" spans="1:4">
@@ -28592,13 +28700,13 @@
         <v>35</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
     </row>
     <row r="37" ht="15.5" spans="1:4">
@@ -28606,13 +28714,13 @@
         <v>36</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
     </row>
     <row r="38" ht="15.5" spans="1:4">
@@ -28620,13 +28728,13 @@
         <v>37</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>289</v>
+        <v>299</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>296</v>
+        <v>306</v>
       </c>
     </row>
     <row r="39" ht="15.5" spans="1:4">
@@ -28634,13 +28742,13 @@
         <v>38</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>298</v>
+        <v>308</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>299</v>
+        <v>309</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>305</v>
+        <v>315</v>
       </c>
     </row>
     <row r="40" ht="15.5" spans="1:4">
@@ -28648,13 +28756,13 @@
         <v>39</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
     </row>
     <row r="41" ht="15.5" spans="1:4">
@@ -28662,10 +28770,10 @@
         <v>40</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>321</v>
+        <v>331</v>
       </c>
       <c r="D41" s="4"/>
     </row>
@@ -28674,13 +28782,13 @@
         <v>41</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>337</v>
+        <v>347</v>
       </c>
     </row>
     <row r="43" ht="15.5" spans="1:4">
@@ -28688,13 +28796,13 @@
         <v>42</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>339</v>
+        <v>349</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>337</v>
+        <v>347</v>
       </c>
     </row>
     <row r="44" ht="15.5" spans="1:4">
@@ -28702,13 +28810,13 @@
         <v>43</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>348</v>
+        <v>358</v>
       </c>
     </row>
     <row r="45" ht="15.5" spans="1:4">
@@ -28716,13 +28824,13 @@
         <v>44</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>351</v>
+        <v>361</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>355</v>
+        <v>365</v>
       </c>
     </row>
     <row r="46" ht="15.5" spans="1:4">
@@ -28730,13 +28838,13 @@
         <v>45</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>357</v>
+        <v>367</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>351</v>
+        <v>361</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>355</v>
+        <v>365</v>
       </c>
     </row>
     <row r="47" ht="15.5" spans="1:4">
@@ -28744,13 +28852,13 @@
         <v>46</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>351</v>
+        <v>361</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>355</v>
+        <v>365</v>
       </c>
     </row>
     <row r="48" ht="15.5" spans="1:4">
@@ -28758,13 +28866,13 @@
         <v>47</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>359</v>
+        <v>369</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>363</v>
+        <v>373</v>
       </c>
     </row>
     <row r="49" ht="15.5" spans="1:4">
@@ -28772,13 +28880,13 @@
         <v>48</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>371</v>
+        <v>381</v>
       </c>
     </row>
     <row r="50" ht="15.5" spans="1:4">
@@ -28786,13 +28894,13 @@
         <v>49</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>373</v>
+        <v>383</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>374</v>
+        <v>384</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>380</v>
+        <v>390</v>
       </c>
     </row>
     <row r="51" ht="15.5" spans="1:4">
@@ -28800,13 +28908,13 @@
         <v>50</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>390</v>
+        <v>400</v>
       </c>
     </row>
     <row r="52" ht="15.5" spans="1:4">
@@ -28814,13 +28922,13 @@
         <v>51</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>392</v>
+        <v>402</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
     </row>
     <row r="53" ht="15.5" spans="1:4">
@@ -28828,13 +28936,13 @@
         <v>52</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>404</v>
+        <v>414</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>406</v>
+        <v>416</v>
       </c>
     </row>
     <row r="54" ht="15.5" spans="1:4">
@@ -28842,13 +28950,13 @@
         <v>53</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>408</v>
+        <v>418</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>409</v>
+        <v>419</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>417</v>
+        <v>427</v>
       </c>
     </row>
     <row r="55" ht="15.5" spans="1:4">
@@ -28856,13 +28964,13 @@
         <v>54</v>
       </c>
       <c r="B55" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="C55" s="4" t="s">
         <v>419</v>
       </c>
-      <c r="C55" s="4" t="s">
-        <v>409</v>
-      </c>
       <c r="D55" s="4" t="s">
-        <v>417</v>
+        <v>427</v>
       </c>
     </row>
     <row r="56" ht="15.5" spans="1:4">
@@ -28870,13 +28978,13 @@
         <v>55</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>420</v>
+        <v>430</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>421</v>
+        <v>431</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>422</v>
+        <v>432</v>
       </c>
     </row>
     <row r="57" ht="15.5" spans="1:4">
@@ -28884,13 +28992,13 @@
         <v>56</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>425</v>
+        <v>435</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>431</v>
+        <v>441</v>
       </c>
     </row>
     <row r="58" ht="15.5" spans="1:4">
@@ -28898,13 +29006,13 @@
         <v>57</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>434</v>
+        <v>444</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>435</v>
+        <v>445</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>436</v>
+        <v>446</v>
       </c>
     </row>
     <row r="59" ht="15.5" spans="1:4">
@@ -28912,13 +29020,13 @@
         <v>58</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>437</v>
+        <v>447</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>435</v>
+        <v>445</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>436</v>
+        <v>446</v>
       </c>
     </row>
     <row r="60" ht="15.5" spans="1:4">
@@ -28926,13 +29034,13 @@
         <v>59</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>439</v>
+        <v>449</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>440</v>
+        <v>450</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>441</v>
+        <v>451</v>
       </c>
     </row>
     <row r="61" ht="15.5" spans="1:4">
@@ -28940,13 +29048,13 @@
         <v>60</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>443</v>
+        <v>453</v>
       </c>
       <c r="D61" t="s">
-        <v>444</v>
+        <v>454</v>
       </c>
     </row>
     <row r="62" ht="15.5" spans="1:4">
@@ -28954,13 +29062,13 @@
         <v>61</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>445</v>
+        <v>455</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>446</v>
+        <v>456</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>447</v>
+        <v>457</v>
       </c>
     </row>
     <row r="63" ht="15.5" spans="1:4">
@@ -28968,13 +29076,13 @@
         <v>62</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>448</v>
+        <v>458</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>449</v>
+        <v>459</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
     </row>
     <row r="64" ht="15.5" spans="1:4">
@@ -28982,13 +29090,13 @@
         <v>63</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>452</v>
+        <v>462</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>453</v>
+        <v>463</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>454</v>
+        <v>464</v>
       </c>
     </row>
     <row r="65" ht="15.5" spans="1:4">
@@ -29009,11 +29117,6 @@
       <c r="C67" s="4"/>
       <c r="D67" s="4"/>
     </row>
-    <row r="68" ht="15.5" spans="1:4">
-      <c r="A68" s="4"/>
-      <c r="B68" s="4"/>
-      <c r="C68" s="4"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/Dataset_inf.xlsx
+++ b/Dataset_inf.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12280"/>
+    <workbookView windowWidth="25600" windowHeight="10480"/>
   </bookViews>
   <sheets>
     <sheet name="Label" sheetId="1" r:id="rId1"/>
@@ -1499,49 +1499,49 @@
     <t>2(Condition:self_Asian vs. self_White)*2(Trials:MatchingnNonmatching)*2(Identity:Self,Other)</t>
   </si>
   <si>
+    <t>Dalmaso_2024_CC</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.17605/OSF.IO/XA4H8</t>
+  </si>
+  <si>
+    <t>Pu2E2</t>
+  </si>
+  <si>
+    <t>Pu3E1</t>
+  </si>
+  <si>
+    <t>Pu3</t>
+  </si>
+  <si>
+    <t>Smith_2024_Cortex</t>
+  </si>
+  <si>
+    <t>https://osf.io/br98c/</t>
+  </si>
+  <si>
+    <t>Pu4E1</t>
+  </si>
+  <si>
+    <t>Pu4</t>
+  </si>
+  <si>
+    <t>Neil W. Kirk</t>
+  </si>
+  <si>
+    <t>n.kirk@abertay.ac.uk</t>
+  </si>
+  <si>
+    <t>Neil W. Kirk et al.</t>
+  </si>
+  <si>
+    <t>British Journal of Psycholog</t>
+  </si>
+  <si>
+    <t>Slef</t>
+  </si>
+  <si>
     <t>voice</t>
-  </si>
-  <si>
-    <t>Dalmaso_2024_CC</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.17605/OSF.IO/XA4H8</t>
-  </si>
-  <si>
-    <t>Pu2E2</t>
-  </si>
-  <si>
-    <t>Pu3E1</t>
-  </si>
-  <si>
-    <t>Pu3</t>
-  </si>
-  <si>
-    <t>Smith_2024_Cortex</t>
-  </si>
-  <si>
-    <t>https://osf.io/br98c/</t>
-  </si>
-  <si>
-    <t>Pu4E1</t>
-  </si>
-  <si>
-    <t>Pu4</t>
-  </si>
-  <si>
-    <t>Neil W. Kirk</t>
-  </si>
-  <si>
-    <t>n.kirk@abertay.ac.uk</t>
-  </si>
-  <si>
-    <t>Neil W. Kirk et al.</t>
-  </si>
-  <si>
-    <t>British Journal of Psycholog</t>
-  </si>
-  <si>
-    <t>Slef</t>
   </si>
   <si>
     <t>Kirk_2025_BJP</t>
@@ -23124,13 +23124,13 @@
         <v>425</v>
       </c>
       <c r="AI58" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="AJ58" s="4" t="s">
         <v>426</v>
       </c>
-      <c r="AJ58" s="4" t="s">
+      <c r="AK58" s="12" t="s">
         <v>427</v>
-      </c>
-      <c r="AK58" s="12" t="s">
-        <v>428</v>
       </c>
       <c r="AL58" s="4" t="s">
         <v>128</v>
@@ -23400,7 +23400,7 @@
         <v>58</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="D59" s="4" t="s">
         <v>419</v>
@@ -23478,13 +23478,13 @@
         <v>425</v>
       </c>
       <c r="AI59" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="AJ59" s="4" t="s">
         <v>426</v>
       </c>
-      <c r="AJ59" s="4" t="s">
+      <c r="AK59" s="12" t="s">
         <v>427</v>
-      </c>
-      <c r="AK59" s="12" t="s">
-        <v>428</v>
       </c>
       <c r="AL59" s="4" t="s">
         <v>128</v>
@@ -23754,10 +23754,10 @@
         <v>59</v>
       </c>
       <c r="C60" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="D60" s="4" t="s">
         <v>430</v>
-      </c>
-      <c r="D60" s="4" t="s">
-        <v>431</v>
       </c>
       <c r="E60" s="8" t="s">
         <v>40</v>
@@ -23801,10 +23801,10 @@
         <v>169</v>
       </c>
       <c r="AJ60" s="4" t="s">
+        <v>431</v>
+      </c>
+      <c r="AK60" s="11" t="s">
         <v>432</v>
-      </c>
-      <c r="AK60" s="11" t="s">
-        <v>433</v>
       </c>
       <c r="AL60" s="4" t="s">
         <v>193</v>
@@ -24074,10 +24074,10 @@
         <v>60</v>
       </c>
       <c r="C61" s="4" t="s">
+        <v>433</v>
+      </c>
+      <c r="D61" s="4" t="s">
         <v>434</v>
-      </c>
-      <c r="D61" s="4" t="s">
-        <v>435</v>
       </c>
       <c r="E61" s="8" t="s">
         <v>40</v>
@@ -24092,19 +24092,19 @@
         <v>0</v>
       </c>
       <c r="I61" s="4" t="s">
+        <v>435</v>
+      </c>
+      <c r="J61" s="11" t="s">
         <v>436</v>
       </c>
-      <c r="J61" s="11" t="s">
+      <c r="K61" s="4" t="s">
         <v>437</v>
-      </c>
-      <c r="K61" s="4" t="s">
-        <v>438</v>
       </c>
       <c r="L61" s="4">
         <v>2024</v>
       </c>
       <c r="M61" s="4" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="N61" s="4">
         <v>1</v>
@@ -24113,7 +24113,7 @@
         <v>1</v>
       </c>
       <c r="P61" s="4" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="Q61" s="4" t="s">
         <v>80</v>
@@ -24138,7 +24138,7 @@
       <c r="AG61" s="4"/>
       <c r="AH61" s="4"/>
       <c r="AI61" s="4" t="s">
-        <v>426</v>
+        <v>440</v>
       </c>
       <c r="AJ61" s="4" t="s">
         <v>441</v>
@@ -24417,7 +24417,7 @@
         <v>443</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E62" s="8" t="s">
         <v>40</v>
@@ -24432,19 +24432,19 @@
         <v>0</v>
       </c>
       <c r="I62" s="4" t="s">
+        <v>435</v>
+      </c>
+      <c r="J62" s="11" t="s">
         <v>436</v>
       </c>
-      <c r="J62" s="11" t="s">
+      <c r="K62" s="4" t="s">
         <v>437</v>
-      </c>
-      <c r="K62" s="4" t="s">
-        <v>438</v>
       </c>
       <c r="L62" s="4">
         <v>2024</v>
       </c>
       <c r="M62" s="4" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="N62" s="4">
         <v>1</v>
@@ -24453,7 +24453,7 @@
         <v>1</v>
       </c>
       <c r="P62" s="4" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="Q62" s="4" t="s">
         <v>80</v>
@@ -24478,7 +24478,7 @@
       <c r="AG62" s="4"/>
       <c r="AH62" s="4"/>
       <c r="AI62" s="4" t="s">
-        <v>426</v>
+        <v>440</v>
       </c>
       <c r="AJ62" s="4" t="s">
         <v>441</v>
@@ -28956,7 +28956,7 @@
         <v>419</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="55" ht="15.5" spans="1:4">
@@ -28964,13 +28964,13 @@
         <v>54</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C55" s="4" t="s">
         <v>419</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="56" ht="15.5" spans="1:4">
@@ -28978,13 +28978,13 @@
         <v>55</v>
       </c>
       <c r="B56" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="C56" s="4" t="s">
         <v>430</v>
       </c>
-      <c r="C56" s="4" t="s">
+      <c r="D56" s="4" t="s">
         <v>431</v>
-      </c>
-      <c r="D56" s="4" t="s">
-        <v>432</v>
       </c>
     </row>
     <row r="57" ht="15.5" spans="1:4">
@@ -28992,10 +28992,10 @@
         <v>56</v>
       </c>
       <c r="B57" s="4" t="s">
+        <v>433</v>
+      </c>
+      <c r="C57" s="4" t="s">
         <v>434</v>
-      </c>
-      <c r="C57" s="4" t="s">
-        <v>435</v>
       </c>
       <c r="D57" s="4" t="s">
         <v>441</v>
